--- a/カロナビ/2026-09-28_カロナビ_リポジトリ別現状整理.xlsx
+++ b/カロナビ/2026-09-28_カロナビ_リポジトリ別現状整理.xlsx
@@ -14,15 +14,15 @@
     <sheet name="lp" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'差分まとめ'!$A$1:$H$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'差分まとめ'!$A$1:$H$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'差分まとめ'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AYG'!$A$1:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AYG'!$A$1:$F$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'AYG'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'org-company'!$A$1:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'org-company'!$A$1:$F$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'org-company'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'company-os'!$A$1:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'company-os'!$A$1:$F$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'company-os'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'lp'!$A$1:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'lp'!$A$1:$F$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'lp'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="111" customHeight="1">
+    <row r="2" ht="126" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>調査範囲</t>
@@ -548,12 +548,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 19:42 JST 時点で、公開リポジトリ naruto-aii/AYG の全リモートブランチ20本と全PR（オープンは Draft 9本: #1 #11 #15 #16 #25 #26 #27 #28 #29）を git と GitHub API で読んだ。アプリコードの先端は Draft PR #29（cursor/apple-token-revoke-on-delete-eb80、48c4255、19:30 JST）。#28（bd3d3cb、19:00 JST）はその1つ下。main は LP と公開法務。web-preview はアプリ土台（9b4c961、09-25）。</t>
+          <t>2026-09-27 19:42 JST 時点で、公開リポジトリ naruto-aii/AYG の全リモートブランチ20本と全PR（オープンは Draft 9本: #1 #11 #15 #16 #25 #26 #27 #28 #29）を git と GitHub API で読んだ。アプリコードの先端は Draft PR #29（cursor/apple-token-revoke-on-delete-eb80、cdecdc7、19:51 JST）。#28（bd3d3cb、19:00 JST）はその下。#29 は 48c4255 の後に文書2件（0efb0de、cdecdc7）が乗っている。main は LP と公開法務。web-preview はアプリ土台（9b4c961、09-25）。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 時点の main 先端は 9f6a176（PR #7 の Note 目標のあと、社長決定で秘書を廃止）。オープンPRは0。カロナビの議事録5本は main にある。リモートブランチは main 以外5本で、いずれも main より先行コミット0（すべて main の祖先）。</t>
+          <t>2026-09-27 時点の main 先端は 0a779bc（秘書廃止のあと、社長補佐の名前をゆりちゃんに変更。役割は同じ、と更新履歴）。オープンPRは0。カロナビの議事録5本は main にある。議事録の文面は「社長補佐」のまま。リモートブランチは main 以外5本で、いずれも main より先行コミット0（すべて main の祖先）。</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -1220,40 +1220,40 @@
       </c>
     </row>
     <row r="20" ht="126" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>機能</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>運動記録・複数種目</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>01_Project: 手入力、運動履歴、消費カロリーの記録。デザイナー仕様 docs/design/03_WORKOUT_INPUT.md（増やさないカタログ）: ウォーキング、ランニング・ジョギング、自転車、水泳、筋トレ、バスケットボール、ヨガ・ストレッチ、家事・掃除、その他（手入力）。筋トレだけ任意で種目ごとのセット・回数・重量を複数。消費カロリーは実施時間から計算し、セット数では計算しない。追加消費は安静時を除いた net。歩きは「追加の運動／いつもの移動」。家事は生活活動係数に含まれる旨の注意。種類チップと検索は出さない。機能は凍結。</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>運動の記録は無料、と境界案。種目一覧は書いていない。</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>種目と時間からの MET 計算か、追加消費 kcal の手入力。ホームの残りに足すのは追加分だけ。通勤や家事のいつもの動きは生活活動の係数に含まれ、追加運動には入れない。対応端末では Apple ヘルスケアから歩数や運動を取り込める。ヘルスケアの当日消費カロリーは参考表示で、食事目標には足さない。</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>種目の固定リストは AYG のデザイン仕様だけ。計算の意味（追加分だけ足す、家事は生活活動）は lp と一致。</t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>種目の固定リストは AYG のデザイン仕様だけ。追加分だけ足す、家事は生活活動、は lp と合う。lp は Apple ヘルスケアから歩数を取り込めると書く。#29 の docs/app-review/demo-account.md と app-privacy-draft.md は、歩数は読まない、と書く。</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="111" customHeight="1">
+    <row r="22" ht="171" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>機能</t>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Owner Decision: Apple Health / Health Connect と連携。利用時は Health データを計算に使う。非利用時は Activity Level。再同期。Web Preview では Health 非対応。Health の Workout を運動履歴へどう反映するかは Open Question（Q4）。entitlements に HealthKit。用途文は目標計算だけ、広告・マーケティングには使わない。法務 README: 実機で Google ログインと Health を通すのが残タスク。初回にやらなくてよい項目に「Health Workout の運動反映」がある。</t>
+          <t>Owner Decision: Apple Health / Health Connect と連携。利用時は Health データを計算に使う。非利用時は Activity Level。再同期。Web Preview では Health 非対応。Health の Workout を運動履歴へどう反映するかは Open Question（Q4）。entitlements に HealthKit。#29 先端（cdecdc7）の用途文は「読み取り、カロリー目標の計算と記録の表示に使う。広告やマーケティングには使わない」。同じ先端の demo-account.md と app-privacy-draft.md は、読むのは生年月日・性別・身長・体重・アクティブエネルギー・ワークアウトだけで、歩数は読まない、書き込み権限は無い、と書く。法務 README: 実機で Google ログインと Health を通すのが残タスク。初回にやらなくてよい項目に「Health Workout の運動反映」がある。</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>AYG の正式スコープは Apple Health と Health Connect の両方。#28 以降のターゲットは iPhone のみで、公開 LP（lp リポジトリ）は Apple ヘルスケアだけを書く。CMO は実機確認まで「連携」と書かない、としているが、lp リポジトリの LP はすでに連携を書いている。</t>
+          <t>AYG の正式スコープは Apple Health と Health Connect。#28 以降は iPhone のみ。lp は歩数や運動を取り込めると書く。#29 先端の審査用メモは歩数を読まないと書く。CMO は実機確認まで「連携」と書かない、としているが、lp はすでに連携を書いている。</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="126" customHeight="1">
+    <row r="39" ht="156" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>プライバシー</t>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>#28/#29 の ios/Runner/PrivacyInfo.xcprivacy。NSPrivacyTracking は false。追跡ドメインなし。Required Reason API: UserDefaults CA92.1、File timestamp C617.1 と 0A2A.1、System boot time 35F9.1、Disk space 7D9E.1。収集データ: メール、ユーザー ID（機能と Analytics）、Health（機能）、Product Interaction（Analytics）。main と web-preview にこのファイルは無い。PR #28 本文は、共有 UserDefaults の用途をサブスク期限、日次の公開食品検索回数、最終ログインユーザー ID と説明。</t>
+          <t>#28 の ios/Runner/PrivacyInfo.xcprivacy。NSPrivacyTracking は false。追跡ドメインなし。Required Reason API: UserDefaults CA92.1、File timestamp C617.1 と 0A2A.1、System boot time 35F9.1、Disk space 7D9E.1。#28 時点の収集データ: メール、ユーザー ID（機能と Analytics）、Health（機能）、Product Interaction（Analytics）。#29 先端 cdecdc7 は、これに Fitness、Purchase History、Other User Content、Other Data Types を足している。main と web-preview にこのファイルは無い。PR #28 本文は、共有 UserDefaults の用途をサブスク期限、日次の公開食品検索回数、最終ログインユーザー ID と説明。</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="156" customHeight="1">
+    <row r="40" ht="180" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>プライバシー</t>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>#29 の legal/privacy.html（ページ上の最終更新日 2026-09-27）: アカウント識別子（Google または Apple、メール）、基本情報と目標、食事・アルコール・運動・体重・保存食品・公開食品、Health または Health Connect、バーコード、Good/Bad・通報・ブロック、問い合わせメール、ストアの購入状態（カード番号は取らない）、利用状況（上限到達と有料切替をユーザー ID に紐づけ）。広告識別子は取らない。Health は広告・マーケティングに使わない。第三者に Google LLC（Google ログイン、Health Connect）。アプリ内課金の第三者としての Google の行は、main の公開版にはあり、#29 版では外している。利用状況の項目は #29 版にあり、公開中の main 版には無い。</t>
+          <t>#29 先端 cdecdc7 の legal/privacy.html: 最終更新日の欄は「【公表日：社長確認後に記入】」。取得は、Google または Apple の識別子、基本情報と目標、食事・アルコール・運動・体重・保存食品・公開食品、Apple Health の読み取り（Health Connect の行は外した）、バーコード、Good/Bad・通報・ブロック、問い合わせ、購入状態（購入の有無と期限だけ。カード番号は取らない）、利用状況（上限に初めて達した日時とカロナビ+へ切り替えた日時。食事内容やレシートは含まない）、Sign in with Apple の更新用トークン（削除時の連携解除のため、暗号化してサーバーに保存）。委託先の国名、Open Food Facts の運営主体と所在国、バックアップ保持日数、開示手数料は「社長確認後に記入」のプレースホルダ。公開中の main 版は Health Connect と Google Play 課金を含み、利用状況と Apple トークンの行は無い。</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2013,73 +2013,73 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>公開中のプライバシー（main）と、未マージのアプリ同梱版（#27 以降）で、利用状況の記録と Google のアプリ内課金の行が違う。lp がリンクしているのは公開中の URL。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="111" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+          <t>公開中のプライバシー（main）と、未マージの #29 先端で、Health Connect の有無、利用状況の範囲、Apple トークン、未記入のプレースホルダが違う。lp がリンクしているのは公開中の URL。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="180" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プライバシー</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>#29 先端の docs/app-review/app-privacy-draft.md。案であり、App Store Connect にはまだ入力していない。弁護士確認はしていない。トラッキングしない。収集する、と書くもの: User ID、Product Interaction（上限に初めて達した日時。Analytics）、Purchase History（有料へ切り替えた日時。レシートや取引 ID は表に入れない）、Email、Health（歩数はリストに無い。ワークアウト行は端末内の Isar だけで収集としては宣言しない）、Fitness（サーバーに残るアクティブエネルギーと運動記録）、Other User Content（保存食品、公開食品、テンプレート、目標、評価、通報、ブロック。写真は保存しない）、Other Data Types（Sign in with Apple の refresh token。保存するので申告する）。収集しない: 位置、連絡先、閲覧履歴、カード番号、クラッシュ、広告 ID、検索履歴、氏名（fullName はスコープにあるが保存しない）。Google の Health Connect は iPhone 提出では使わない、と書く。Supabase の保存先リージョンはリポジトリからは特定できない、と書く。</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案は 10/5 までに CTO が作る。利用データ（利用者に紐づく）が加わる見込み、と CTO-CPO 議事録。</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>一部にしか記載なし</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>回答案のファイルは #29 にある。org の期限は 10/5。入力済みとは書いていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="111" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>法務</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>法務ページの置き場（2系統）</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>公開中は main の docs/legal/ を https://naruto-aii.github.io/AYG/legal/ に出す（目次、privacy、terms、tokushoho、support、account-deletion）。アプリ同梱は #29 の legal/ 以下の同じ6ファイルで、アプリ内は全画面表示。外部リンクは Safari、と org が CTO 確認として記録。01_Project: 公開 HTML の原稿は legal/。弁護士確認は未実施、と法務 README。参照した公開書類: あすけん、カロミル、FiNC、消費者庁・特商法11条、個人情報保護法。</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>サポート URL は naruto-aii.github.io/AYG/legal/ を使う案 A。場所を変えない。</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>法務リンクは naruto-aii.github.io/AYG/legal 。lp リポジトリ内に規約本文は無い。</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>食い違い</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>URL は AYG main・org・lp で同じ公開 URL。中身は AYG の main（公開中）と未マージの legal/ で違う（価格の書き方、Google Play、利用状況、削除済みユーザー、日付）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="126" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>法務</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>利用規約の記載</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>法務 README が埋めた項目: 適用、定義、非医療、アカウント、未成年、課金・定期購入の解約、公開食品の利用許諾、禁止、知財、退会、非保証、損害賠償の上限、反社、地位譲渡、分離可能性、変更、準拠法。#29 の terms: 運営は麹池成、ストアは現在 App Store、日本法、東京地方裁判所を第一審の専属的合意管轄。公開食品は削除後も残り、作成者欄は「削除済みユーザー」。main の公開 terms はストアを App Store または Google Play とし、「削除済みユーザー」の文は #29 との diff で追加側（公開版にはその文が無い）。</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>記載なし（条文の写しは無い）。</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>条文は無く、公開法務 URL へリンク。</t>
+          <t>法務リンクは naruto-aii.github.io/AYG/legal 。lp リポジトリ内に規約本文は無い。</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2089,11 +2089,11 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>公開中の規約と未マージの規約で、ストア（Google Play の有無）と削除後の作成者表示が違う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="171" customHeight="1">
+          <t>URL は AYG main・org・lp で同じ公開 URL。中身は AYG の main（公開中）と未マージの legal/ で違う（価格の書き方、Google Play、利用状況、削除済みユーザー、日付）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="126" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>法務</t>
@@ -2101,23 +2101,23 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>特定商取引法の記載</t>
+          <t>利用規約の記載</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>共通: 販売業者 麹池成、住所は東京都で請求と本人確認のうえ開示、電話も請求開示、メール calonavi.ayg.support@gmail.com、送料なし、通信料は利用者、提供は決済後すぐ、申込期限なし、返品は原則不可で返金はストア、定期購入の解約はストア（アプリ削除・ログアウト・アカウント削除では止まらない）。違い: 公開中（main、ページ上 2026-09-20）は支払方法が App Store または Google Play、動作環境は iOS または Android、販売価格は「各購入画面に税込で表示」。未マージ（#29、ページ上 2026-09-27）は支払方法が App Store、動作環境は App Store の iOS、販売価格は「App Store の購入画面に表示される価格。このページでは金額を定めません」。380 円も 480 円も特商法 HTML には書いていない。</t>
+          <t>法務 README が埋めた項目: 適用、定義、非医療、アカウント、未成年、課金・定期購入の解約、公開食品の利用許諾、禁止、知財、退会、非保証、損害賠償の上限、反社、地位譲渡、分離可能性、変更、準拠法。#29 の terms: 運営は麹池成、ストアは現在 App Store、日本法、東京地方裁判所を第一審の専属的合意管轄。公開食品は削除後も残り、作成者欄は「削除済みユーザー」。main の公開 terms はストアを App Store または Google Play とし、「削除済みユーザー」の文は #29 との diff で追加側（公開版にはその文が無い）。</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>特商法の条文写しは無い。値段は社長未決。</t>
+          <t>記載なし（条文の写しは無い）。</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>特商法の本文は無い。料金はストア画面が正、と LP が書く。</t>
+          <t>条文は無く、公開法務 URL へリンク。</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>公開中の特商法と未マージの特商法で、Google Play の有無と動作環境と価格の言い回しが違う。金額の数字はどちらの特商法にも無い。数字は社内メモと公開 LP 側にある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="111" customHeight="1">
+          <t>公開中の規約と未マージの規約で、ストア（Google Play の有無）と削除後の作成者表示が違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="171" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>法務</t>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>アカウント削除の法務文</t>
+          <t>特定商取引法の記載</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>アプリ内: ログイン、設定、アカウント削除、案内を確認して実行。メール: ログインに使ったアドレスから件名「アカウント削除」。消えるもの: 食事・運動・体重などの個人記録、非公開の保存食品、食事テンプレート、プロフィール、目標、Health の個人向けデータ。残るもの: 公開食品。#29 版は作成者欄を「削除済みユーザー」。公開中の main 版は氏名やメールを載せない、までで、その「削除済みユーザー」の文は diff 上 #29 側だけ。課金は自動では止まらない。</t>
+          <t>共通: 販売業者 麹池成、住所は東京都で請求と本人確認のうえ開示、電話も請求開示、メール calonavi.ayg.support@gmail.com、送料なし、通信料は利用者、提供は決済後すぐ、申込期限なし、返品は原則不可で返金はストア、定期購入の解約はストア（アプリ削除・ログアウト・アカウント削除では止まらない）。違い: 公開中（main、ページ上 2026-09-20）は支払方法が App Store または Google Play、動作環境は iOS または Android、販売価格は「各購入画面に税込で表示」。未マージ（#29、ページ上 2026-09-27）は支払方法が App Store、動作環境は App Store の iOS、販売価格は「App Store の購入画面に表示される価格。このページでは金額を定めません」。380 円も 480 円も特商法 HTML には書いていない。</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>削除後の公開食品は残し、作成者欄は「削除済みユーザー」、と法務 README の決定を org は直接は書いていない。CPO はアカウント削除を無料機能に数えている。</t>
+          <t>特商法の条文写しは無い。値段は社長未決。</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>特商法の本文は無い。料金はストア画面が正、と LP が書く。</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2165,187 +2165,187 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>「削除済みユーザー」は未マージの法務 HTML と AYG の法務 README にある。公開中の account-deletion.html にはその文言が無い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="141" customHeight="1">
+          <t>公開中の特商法と未マージの特商法で、Google Play の有無と動作環境と価格の言い回しが違う。金額の数字はどちらの特商法にも無い。数字は社内メモと公開 LP 側にある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="126" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ストア</t>
+          <t>法務</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>掲載文・キーワード</t>
+          <t>アカウント削除の法務文</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>草案は PR #1 の docs/store/APP_STORE_LISTING.md のみ（#28/#29 には無い）。プロモーション文、説明、What's New、キーワード草案（カロリー,食事,運動,体重,ダイエット,PFC,タンパク質,減量,増量,ヘルスケア,記録,エネルギー）。書いてはいけないこと: 店名の AYG、治療・診断、課金や広告があるかのような表現、ゲスト・英語・Android 先行、サポート URL を確定したかのような記述、法務文面を確定と書くこと。法務 README の残タスク: 掲載テキスト（URL、年齢、Privacy Nutrition Labels、審査メモ）。スクショとアイコンは空のまま、と README。</t>
+          <t>アプリ内: ログイン、設定、アカウント削除、案内を確認して実行。メール: ログインに使ったアドレスから件名「アカウント削除」。消えるもの: 食事・運動・体重などの個人記録、非公開の保存食品、食事テンプレート、プロフィール、目標、Health の個人向けデータ。#29 先端は、アカウント情報（メールアドレス等）と利用状況の記録、Sign in with Apple の連携解除を消えるものに足している。残るもの: 公開食品。#29 版は作成者欄を「削除済みユーザー」。公開中の main 版にはその文が無い。課金は自動では止まらない。</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>CMO 議事録の決定: 数値は必ず「目安」、医療機器でない旨、効果・病名・根拠のない実績は使わない、有料プランの存在は明記、「ダイエット」はキーワード欄で可。ヘルスケアは 10/5 まで「連携」と書かない。4+ は使わない。ストア掲載文の期限は CMO 目標で 10/6。健康表現の最終線引きと、価格未定時の料金の書き方は 10/6 の掲載文完成時に社長へ。</t>
+          <t>削除後の公開食品は残し、作成者欄は「削除済みユーザー」、と法務 README の決定を org は直接は書いていない。CPO はアカウント削除を無料機能に数えている。</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>「削除済みユーザー」は未マージの法務 HTML と AYG の法務 README にある。公開中の account-deletion.html にはその文言が無い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="141" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>掲載文・キーワード</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>草案は PR #1 の docs/store/APP_STORE_LISTING.md のみ（#28/#29 には無い）。プロモーション文、説明、What's New、キーワード草案（カロリー,食事,運動,体重,ダイエット,PFC,タンパク質,減量,増量,ヘルスケア,記録,エネルギー）。書いてはいけないこと: 店名の AYG、治療・診断、課金や広告があるかのような表現、ゲスト・英語・Android 先行、サポート URL を確定したかのような記述、法務文面を確定と書くこと。法務 README の残タスク: 掲載テキスト（URL、年齢、Privacy Nutrition Labels、審査メモ）。スクショとアイコンは空のまま、と README。</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>CMO 議事録の決定: 数値は必ず「目安」、医療機器でない旨、効果・病名・根拠のない実績は使わない、有料プランの存在は明記、「ダイエット」はキーワード欄で可。ヘルスケアは 10/5 まで「連携」と書かない。4+ は使わない。ストア掲載文の期限は CMO 目標で 10/6。健康表現の最終線引きと、価格未定時の料金の書き方は 10/6 の掲載文完成時に社長へ。</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
           <t>LP はストア掲載文ではない。</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>食い違い</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>PR #1 草案は課金があるかのように書くのを禁じ、年齢案は 4+。CMO 議事録は有料プランの存在を明記し、4+ は使わない。草案は #1 ブランチにしか無い。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="96" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47" ht="96" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>スクリーンショット・アイコン</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>iOS の AppIcon.appiconset に 1024 を含む PNG がある。assets/brand/app_icon_placeholder.svg がある。法務 README: スクリーンショットとアイコンは空のまま先にテキストだけ入れる。見た目・アイコン・スクショ・TestFlight はデザイン後。PR #1 にスクショ用コピー5行（今日あと何kcal、食事は打つ・撮る・選ぶ、運動、体重、根拠）。ストア用スクショ画像のセットはリポジトリに無い。</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>アイコン3案から1つを社長が選ぶ（9/30）。1024×1024 の PNG、透過なしを 10/2 までに CTO へ。アイコンとスクリーンショットは CPO 目標で 10/5 まで。3案の画像ファイルは org-company には無い。</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>写真9枚（hero-morning、morning-scale、barcode-scan、worry-fridge、worry-lunch、worry-gym、walk-street、evening-drink、quiet-return）と favicon.svg。ストアのスクリーンショット枠ではない。</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>一部にしか記載なし</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>ストア提出用の確定アイコンとスクショは、読めたリポジトリには揃っていない。lp の画像は LP 用の写真。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="81" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="48" ht="180" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>審査用デモアカウント</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>#29 先端の docs/app-review/demo-account.md。App Review 用。本番 Supabase で作り、パスワードと Sandbox のパスワードと Apple の秘密鍵はファイルに書かない。ログインは Sign in with Apple と Google のみ。メールとパスワードのログインは無い。審査用の共有アカウントは Google で作る。ストア名は「カロナビ - 食事と運動」。Bundle ID は com.narutoaii.ayg。提出ビルドは iPhone のみ。サンプルは、今日の食事とアルコール、ウォーキング 30 分、体重、バーコード（画像は保存しない）、Health の読み取り、カロナビ+ の Sandbox 購入と復元。価格はこの文書では固定しない。無料枠は検索 5 回/日、食事テンプレート 3、運動テンプレート 3。上限に達した回数そのものはサーバーに保存せず、初めて達した日時と有料へ切り替えた日時だけ。審査中はデモアカウントを削除しない。main と web-preview にこのファイルは無い。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>提出準備: 手順とサンプルデータは CTO が用意。本番での作成は 10/6、社長の承認後。</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>一部にしか記載なし</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>手順の文書は未マージの #29 にある。本番作成は org が社長承認後の 10/6 としている。アカウントの中身（メールとパスワード）はどちらのリポジトリにも書いていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="81" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>公開 URL とページの数</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>README（web-preview/#29）: 公開 Preview は https://naruto-aii.github.io/AYG/ 、ランディングページは https://naruto-aii.github.io/AYG/lp/ 。main の docs/index.html がその LP。sitemap は /lp/ と /legal/。workflow は Pages ルートを web-preview、LP を /lp/、法務を /legal/。</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>LP の URL を議事録は一つに決めていない。CPO は「LP に書いた値段」と言う。CMO 目標に「価格決定後の LP 修正」。</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>README: カロナビは https://naruto-aii.github.io/lp/calonavi/ 。sitemap の loc も同じ。更新日 2026-09-25。</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>食い違い</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>公開されている LP が二つある。AYG の /AYG/lp/ と、lp リポジトリの /lp/calonavi/。文言と価格の書き方が違う（次の行）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="81" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>「App Storeで公開中」の表記</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>main の docs/index.html: 「App Storeで公開中（リンク準備中）」。FAQ「いつ使えますか？」の答えは「App Storeで公開しています。」法務 README の残タスクは TestFlight の前（アイコンとスクショが揃ってから出す）。01_Project は App Store での公開を予定、と書く。</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>COO 目標: 2026-10-09 までに App Store 申請（計画は 10/7 申請、10/8-9 予備）。申請はこれから、という日程。</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>「いつ使えますか？」は「App Storeで公開しています。このページからのストアリンクは、いま準備中です。」末尾も「App Storeで公開中です。ストアへのリンクは準備中です。」Information の提供欄も同じ。</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>食い違い</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>二つの LP は公開中と書く。org の目標と AYG の法務 README は、申請・TestFlight がこれからの日程。ストアリンクは両 LP とも準備中。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="66" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>価格の書き方</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>AYG の /lp/: 予定価格（作業ベース）月額 480 円／年額 4,800 円。最終は App Store の購入画面が正。無料の目安は検索 5 回/日、食事テンプレート 3、運動テンプレート 3。カロナビ+ は上限を拡大、と書く。</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>CMO の役割: 値段が決まっていなければ未定と書く。CFO: 決まるまでアプリと LP の表記は触らない。</t>
         </is>
       </c>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>金額は断定しない。有料機能の価格はストアの購入画面が正。無料枠の回数も書かない。</t>
+          <t>README: カロナビは https://naruto-aii.github.io/lp/calonavi/ 。sitemap の loc も同じ。更新日 2026-09-25。</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>AYG の LP は 480/4,800 を予定価格として書く。lp リポジトリは金額を書かない。org は未定なら未定と書き、決まるまで表記を変えるな、としている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="96" customHeight="1">
+          <t>公開されている LP が二つある。AYG の /AYG/lp/ と、lp リポジトリの /lp/calonavi/。文言と価格の書き方が違う（次の行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="81" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>LP</t>
@@ -2367,23 +2367,23 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>機能説明の差（繰り越し・写真解析）</t>
+          <t>「App Storeで公開中」の表記</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>main の LP: 見る・入れる・戻す。アルコールは別記録。運動は MET または kcal 直接入力。体重の一覧・追加・編集・削除。ログインは Google または Apple。向いていない人に、写真自動解析だけが欲しい方（現状の主機能ではない）、ゲストのまま使いたい方。超過の翌日繰り越しが無い、とはこの LP は書いていない（「戻す — 食べ過ぎた日も超過を事実として見て、次の日の感覚を残す」）。</t>
+          <t>main の docs/index.html: 「App Storeで公開中（リンク準備中）」。FAQ「いつ使えますか？」の答えは「App Storeで公開しています。」法務 README の残タスクは TestFlight の前（アイコンとスクショが揃ってから出す）。01_Project は App Store での公開を予定、と書く。</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>COO 目標: 2026-10-09 までに App Store 申請（計画は 10/7 申請、10/8-9 予備）。申請はこれから、という日程。</t>
         </is>
       </c>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>超過を翌日へ繰り越す機能は無い、と繰り返し書く。写真自動解析は実装されていない。未来の日付には記録できない。ゲスト利用は無い。</t>
+          <t>「いつ使えますか？」は「App Storeで公開しています。このページからのストアリンクは、いま準備中です。」末尾も「App Storeで公開中です。ストアへのリンクは準備中です。」Information の提供欄も同じ。</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -2393,149 +2393,149 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>翌日への繰り越しが無いことは lp リポジトリが明示し、AYG main の LP は「次の日の感覚を残す」と書くだけで、繰り越し機能が無いとは書いていない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="96" customHeight="1">
+          <t>二つの LP は公開中と書く。org の目標と AYG の法務 README は、申請・TestFlight がこれからの日程。ストアリンクは両 LP とも準備中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="66" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>サポート</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>窓口のメールと URL</t>
+          <t>価格の書き方</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>calonavi.ayg.support@gmail.com。公開 URL https://naruto-aii.github.io/AYG/legal/support.html 。受付は順次、数日以内を目安。アカウントの依頼はログインに使っているメールから。法務 README: 新しい仕組みは作らない。その Gmail を見られればよい。</t>
+          <t>AYG の /lp/: 予定価格（作業ベース）月額 480 円／年額 4,800 円。最終は App Store の購入画面が正。無料の目安は検索 5 回/日、食事テンプレート 3、運動テンプレート 3。カロナビ+ は上限を拡大、と書く。</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>案 A: 今のサポートページと同じ Gmail を使う。案 B（URL を変える）は採らない前提。誰が Gmail を読むか（社長が読む／CCO 側で下書きまで、送信は社長）は社長判断。返信の目安日数も社長判断。CCO の窓口案は 10/2 まで（提出済み、と議事録）。設定画面から窓口へのリンクは v1 に含める。既存の仕組みを使える、と CTO。</t>
+          <t>CMO の役割: 値段が決まっていなければ未定と書く。CFO: 決まるまでアプリと LP の表記は触らない。</t>
         </is>
       </c>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
+          <t>金額は断定しない。有料機能の価格はストアの購入画面が正。無料枠の回数も書かない。</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>AYG の LP は 480/4,800 を予定価格として書く。lp リポジトリは金額を書かない。org は未定なら未定と書き、決まるまで表記を変えるな、としている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="96" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>機能説明の差（繰り越し・写真解析）</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>main の LP: 見る・入れる・戻す。アルコールは別記録。運動は MET または kcal 直接入力。体重の一覧・追加・編集・削除。ログインは Google または Apple。向いていない人に、写真自動解析だけが欲しい方（現状の主機能ではない）、ゲストのまま使いたい方。超過の翌日繰り越しが無い、とはこの LP は書いていない（「戻す — 食べ過ぎた日も超過を事実として見て、次の日の感覚を残す」）。</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>超過を翌日へ繰り越す機能は無い、と繰り返し書く。写真自動解析は実装されていない。未来の日付には記録できない。ゲスト利用は無い。</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>翌日への繰り越しが無いことは lp リポジトリが明示し、AYG main の LP は「次の日の感覚を残す」と書くだけで、繰り越し機能が無いとは書いていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="96" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>サポート</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>窓口のメールと URL</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>calonavi.ayg.support@gmail.com。公開 URL https://naruto-aii.github.io/AYG/legal/support.html 。受付は順次、数日以内を目安。アカウントの依頼はログインに使っているメールから。法務 README: 新しい仕組みは作らない。その Gmail を見られればよい。</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>案 A: 今のサポートページと同じ Gmail を使う。案 B（URL を変える）は採らない前提。誰が Gmail を読むか（社長が読む／CCO 側で下書きまで、送信は社長）は社長判断。返信の目安日数も社長判断。CCO の窓口案は 10/2 まで（提出済み、と議事録）。設定画面から窓口へのリンクは v1 に含める。既存の仕組みを使える、と CTO。</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
           <t>問い合わせは同じ Gmail。サポートページの本文は置かず、法務 URL へリンク。</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>食い違い</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>メールアドレスは一致。公開サポートページは「数日以内を目安」と書き、org の議事録は返信の目安日数を社長未決としている。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="81" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54" ht="81" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>公開URL</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>いま開く URL</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>https://naruto-aii.github.io/AYG/ （web-preview 由来の Web プレビュー。2026-09-27 に HTTP 200）。https://naruto-aii.github.io/AYG/lp/ （main の LP。200）。https://naruto-aii.github.io/AYG/legal/ 以下（main の法務。特商法は 200 で Google Play の行あり）。</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>議事録が参照する URL は naruto-aii.github.io/AYG/legal/ 。</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>https://naruto-aii.github.io/lp/calonavi/ （200）。</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>一部にしか記載なし</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>URL の役割が分かれている。company-os の /cm/ は 404 で、この環境ではページもリポジトリも読めなかった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="96" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>main と web-preview の分け方</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>既定ブランチは main。publish-pages.yml: アプリ本体は main に merge しない。Pages のルートは常に web-preview。main の README は Flutter の初期文。web-preview と #29 の README は先頭がカロナビの説明で、その下に Flutter 初期文が残る。main に docs/01_Project.md は無い。web-preview の先端は 9b4c961（2026-09-25、PR #23 マージ）。main の先端は c6d5c6e（2026-09-25、PR #24 マージ）。</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>一部にしか記載なし</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>AYG の中の運用。既定ブランチを開くとアプリの README も 01_Project も無い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="126" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>すべて Draft、未マージ。#25 integrate-pr11-web-preview-eb80 → web-preview（947a8b1）。#26 public-food-banned-names-eb80 → #25 のブランチ（3035c58）。#27 calonavi-plus-paywall-eb80 → #26 のブランチ（c03dd07）。#28 ios-privacy-iphone-only-eb80 → #27 のブランチ（bd3d3cb）。#29 apple-token-revoke-on-delete-eb80 → #28 のブランチ（48c4255）。2026-09-27 19:42 JST 時点で #25 と #26 の先端は #28 の祖先（#28 に入っていないコミットは 0）。#29 が #28 の1コミット先。</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>議事録は PR #11 の合流に触れる。#25〜#29 の番号は書いていない。</t>
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>https://naruto-aii.github.io/lp/calonavi/ （200）。</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2545,11 +2545,11 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>積み重ねの先端は #29。#28 はプライバシーと iPhone 限定。ユーザー依頼時点の「#28 が最新」より後に #29 が開いている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="171" customHeight="1">
+          <t>URL の役割が分かれている。company-os の /cm/ は 404 で、この環境ではページもリポジトリも読めなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="96" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
+          <t>main と web-preview の分け方</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>旧先端 70f0bb0（2026-09-27 09:27 UTC、fix: add the iOS privacy manifest and ship iPhone-only）から見て、#26 ブランチ側にだけあったコミットは次の4つ。947a8b1（#25、18:39 JST）fix: show Japanese errors and note that revert keeps applied columns。0b59956（#26、18:43 JST）feat: reject banned words in public food names。94ab79c（#26、18:43 JST）fix: check every public food text field after NFKC folding。3035c58（#26、18:50 JST）fix: accept ordinary foods and compose halfwidth voiced marks。現在の #28（bd3d3cb、19:00 JST）は rebase 後で、この4つを祖先に含む。70f0bb0 側にだけあったコミット（70f0bb0、e81c320、11619dc、ab95e99、931019c）は現在の #28 の歴史には無い。</t>
+          <t>既定ブランチは main。publish-pages.yml: アプリ本体は main に merge しない。Pages のルートは常に web-preview。main の README は Flutter の初期文。web-preview と #29 の README は先頭がカロナビの説明で、その下に Flutter 初期文が残る。main に docs/01_Project.md は無い。web-preview の先端は 9b4c961（2026-09-25、PR #23 マージ）。main の先端は c6d5c6e（2026-09-25、PR #24 マージ）。</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>依頼文の「#28 に入っていない4件」は、旧先端 70f0bb0 に対しては事実。19:00 JST の bd3d3cb 以降は、その4件を含んだ状態。加えて #29 が #28 に無い1件。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="156" customHeight="1">
+          <t>AYG の中の運用。既定ブランチを開くとアプリの README も 01_Project も無い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="141" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -2595,17 +2595,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>古い Draft PR（#1 #11 #15 #16）</t>
+          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>#1 designer-brief-08a9 → main。デザイナー要件、ストア掲載文草案、法務 Markdown。main に無いコミットが5。更新 09-20。#11 legal-pages-and-public-food-ab66 → web-preview。アカウント削除、カロナビ+、Apple ログイン。先端 5f6e87a は #25 の祖先（#25 に含まれ、#11 だけにあるコミットは 0）。オープンのまま。#15 setup-flutter-cloud-env-96c6 → #11 のブランチ。Isar ネイティブ lib の ignore 等、#29 に無いコミットが3（2ceaec2、1783bf5、373da7c）。#16 figma-visual-design-ab66 → web-preview。#29 に無いコミットが2（910abf3 feat: apply delivered Figma visual system、ef563e6 fix: match Figma inspect values）。</t>
+          <t>すべて Draft、未マージ。#25 integrate-pr11-web-preview-eb80 → web-preview（947a8b1）。#26 public-food-banned-names-eb80 → #25 のブランチ（3035c58）。#27 calonavi-plus-paywall-eb80 → #26 のブランチ（c03dd07）。#28 ios-privacy-iphone-only-eb80 → #27 のブランチ（bd3d3cb）。#29 apple-token-revoke-on-delete-eb80 → #28 のブランチ。先端は cdecdc7（19:51 JST）。その下は 0efb0de（19:37 JST）と 48c4255（19:30 JST）。2026-09-27 19:51 JST 時点で #25 と #26 の先端は #28 の祖先（#28 に入っていないコミットは 0）。#29 は #28 より3コミット先。</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PR #11 合流、という言及のみ。</t>
+          <t>議事録は PR #11 の合流に触れる。#25〜#29 の番号は書いていない。</t>
         </is>
       </c>
       <c r="E56" s="2" t="n"/>
@@ -2621,11 +2621,11 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>#11 の内容は #25 以降に入っているが PR は開いたまま。#1 #15 #16 にはスタックに入っていないコミットがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="111" customHeight="1">
+          <t>積み重ねの先端は #29。#28 はプライバシーと iPhone 限定。ユーザー依頼時点の「#28 が最新」より後に #29 が開いている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="171" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -2633,23 +2633,23 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>マージ済みで先端に差が無いブランチ</t>
+          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>web-preview の祖先: feature/v1.1-food-master-supabase、workout-input-redesign、workout-input-simplify、workout-design-brief（PR #12 #13 #14 はマージ済み）。main の祖先: lp-v2-landing-c48e（PR #22）、価格文言の PR #20 #21、LP 公開の #17〜#19、split-lp の #24。pages-keep-web-root は web-preview に #23 でマージ済み。fix-web-preview-deploy と main-web-preview-workflow は 09-19 のデプロイ修正ブランチで、オープン PR は無い。</t>
+          <t>旧先端 70f0bb0（2026-09-27 09:27 UTC、fix: add the iOS privacy manifest and ship iPhone-only）から見て、#26 ブランチ側にだけあったコミットは次の4つ。947a8b1（#25、18:39 JST）fix: show Japanese errors and note that revert keeps applied columns。0b59956（#26、18:43 JST）feat: reject banned words in public food names。94ab79c（#26、18:43 JST）fix: check every public food text field after NFKC folding。3035c58（#26、18:50 JST）fix: accept ordinary foods and compose halfwidth voiced marks。現在の #28（bd3d3cb、19:00 JST）は rebase 後で、この4つを祖先に含む。70f0bb0 側にだけあったコミット（70f0bb0、e81c320、11619dc、ab95e99、931019c）は現在の #28 の歴史には無い。</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>オープン PR は無い。マージ済みは #1 組織記録、#2 COO/CMO 目標、#3 カロナビ目標と運用ルール、#4 議事録3件、#5 書式、#6 議事録5件の全文、#7 Note 目標。main 以外の5ブランチは先行コミット 0。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>PR は 0。main のみ。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -2659,35 +2659,35 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>各リポジトリの PR の有無は事実として並記。内容の矛盾ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="96" customHeight="1">
+          <t>依頼文の「#28 に入っていない4件」は、旧先端 70f0bb0 に対しては事実。19:00 JST の bd3d3cb 以降は、その4件を含んだ状態。加えて #29 が #28 に無い1件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="156" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>開発状況</t>
+          <t>ブランチ・PR</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>法務 README が「済んでいる」とするもの</t>
+          <t>古い Draft PR（#1 #11 #15 #16）</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>法務 HTML とアプリ内全画面、Sign in with Apple（Developer Key、Supabase Apple Enabled、アプリ配線。Web プレビューでは使えない）、アカウント削除 UI と本番 RPC、カロナビ+ のアプリ側と ASC 商品、ストアのアプリ枠（名前はカロナビ - 食事と運動）、公開食品の作成者欄「削除済みユーザー」、通報・作成者ブロック。機能は凍結済み。デザイナーへ見た目を依頼中。</t>
+          <t>#1 designer-brief-08a9 → main。デザイナー要件、ストア掲載文草案、法務 Markdown。main に無いコミットが5。更新 09-20。#11 legal-pages-and-public-food-ab66 → web-preview。アカウント削除、カロナビ+、Apple ログイン。先端 5f6e87a は #25 の祖先（#25 に含まれ、#11 だけにあるコミットは 0）。オープンのまま。#15 setup-flutter-cloud-env-96c6 → #11 のブランチ。Isar ネイティブ lib の ignore 等、#29 に無いコミットが3（2ceaec2、1783bf5、373da7c）。#16 figma-visual-design-ab66 → web-preview。#29 に無いコミットが2（910abf3 feat: apply delivered Figma visual system、ef563e6 fix: match Figma inspect values）。</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CTO の現状欄は「記録なし（2026-09-27時点）」。完了／未完のチェックリストは議事録の期限として書かれる。</t>
+          <t>PR #11 合流、という言及のみ。</t>
         </is>
       </c>
       <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>LP の「いまできること」は出荷済み機能だけ、というコミットメッセージ。コードの完了判定は書いていない。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2697,35 +2697,35 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>完了の自己申告は AYG の法務 README。実機確認は別行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="171" customHeight="1">
+          <t>#11 の内容は #25 以降に入っているが PR は開いたまま。#1 #15 #16 にはスタックに入っていないコミットがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="111" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>開発状況</t>
+          <t>ブランチ・PR</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>実機未確認と残タスク</t>
+          <t>マージ済みで先端に差が無いブランチ</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>法務 README: 実機の機能確認は未完。仮デザインのまま。購入含む。残りの実機確認: Apple ログイン、キーボード、筋トレ複数種目、バーコードカメラ、アカウント削除、公開食品の「削除済みユーザー」、検索5回とテンプレ3件、カロナビ+ の購入と復元（Sandbox）。Google ログインと Health を実機で通す手順は docs/setup/ios_google_health.md（Bundle ID com.narutoaii.ayg、Redirect com.narutoaii.ayg://login-callback、HealthKit capability）。デザイン後: 見た目、アイコン、スクショ、見た目込みの実機、TestFlight → 審査。初回にやらなくてよい: Google Play、法人名義、体重タブの機能追加、Health Workout の運動反映、写真解析、Apple token 失効、レシートのサーバ検証。</t>
+          <t>web-preview の祖先: feature/v1.1-food-master-supabase、workout-input-redesign、workout-input-simplify、workout-design-brief（PR #12 #13 #14 はマージ済み）。main の祖先: lp-v2-landing-c48e（PR #22）、価格文言の PR #20 #21、LP 公開の #17〜#19、split-lp の #24。pages-keep-web-root は web-preview に #23 でマージ済み。fix-web-preview-deploy と main-web-preview-workflow は 09-19 のデプロイ修正ブランチで、オープン PR は無い。</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>実機確認は 10/4〜5（ヘルスケア）。ヘルスケアを「連携」と書くのは 10/5 まで待つ、と CMO。デモアカウントは手順とサンプルを CTO が用意し、本番作成は 10/6、社長承認後。</t>
+          <t>オープン PR は無い。マージ済みは #1 組織記録、#2 COO/CMO 目標、#3 カロナビ目標と運用ルール、#4 議事録3件、#5 書式、#6 議事録5件の全文、#7 Note 目標。main 以外の5ブランチは先行コミット 0。</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>PR は 0。main のみ。</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -2735,35 +2735,35 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>未確認の一覧は AYG。日程は org。Apple token 失効を「やらなくてよい」とする README と、#29 および org の 10/2 は別行の食い違い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="81" customHeight="1">
+          <t>各リポジトリの PR の有無は事実として並記。内容の矛盾ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="96" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>開発状況</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>申請日</t>
+          <t>法務 README が「済んでいる」とするもの</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>日付の記載は法務 README には無い。TestFlight → 審査提出は、アイコンとスクショが揃ってから、とだけ書く。</t>
+          <t>法務 HTML とアプリ内全画面、Sign in with Apple（Developer Key、Supabase Apple Enabled、アプリ配線。Web プレビューでは使えない）、アカウント削除 UI と本番 RPC、カロナビ+ のアプリ側と ASC 商品、ストアのアプリ枠（名前はカロナビ - 食事と運動）、公開食品の作成者欄「削除済みユーザー」、通報・作成者ブロック。機能は凍結済み。デザイナーへ見た目を依頼中。</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>COO: 2026-10-09 までに App Store 申請。計画は 10/7 申請、10/8-9 予備。CTO 目標: 10/7 に審査に通る状態で申請できるようにする。提出準備の議事録: 10/7 に審査で落ちない状態で提出する（期限 10/9）。承認事項のとりまとめ締めは 10/3。</t>
+          <t>CTO の現状欄は「記録なし（2026-09-27時点）」。完了／未完のチェックリストは議事録の期限として書かれる。</t>
         </is>
       </c>
       <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>LP の「いまできること」は出荷済み機能だけ、というコミットメッセージ。コードの完了判定は書いていない。</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2773,29 +2773,29 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>日付は org-company のみ。10/7 と 10/9 は「計画の申請日」と「期限」として両方書いてある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="111" customHeight="1">
+          <t>完了の自己申告は AYG の法務 README。実機確認は別行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="171" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>開発状況</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>10/1 前後の期限</t>
+          <t>実機未確認と残タスク</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>購入画面の実装コミットは 2026-09-27 18:51〜18:59 JST に #27 ブランチへ入っている（#28/#29 に含まれる）。本番適用はしていない、と PR の積み方。</t>
+          <t>法務 README: 実機の機能確認は未完。仮デザインのまま。購入含む。残りの実機確認: Apple ログイン、キーボード、筋トレ複数種目、バーコードカメラ、アカウント削除、公開食品の「削除済みユーザー」、検索5回とテンプレ3件、カロナビ+ の購入と復元（Sandbox）。Google ログインと Health を実機で通す手順は docs/setup/ios_google_health.md（Bundle ID com.narutoaii.ayg、Redirect com.narutoaii.ayg://login-callback、HealthKit capability）。デザイン後: 見た目、アイコン、スクショ、見た目込みの実機、TestFlight → 審査。初回にやらなくてよい: Google Play、法人名義、体重タブの機能追加、Health Workout の運動反映、写真解析、Apple token 失効、レシートのサーバ検証。</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>10/1: カロナビ+ 購入画面（CTO-CPO）。CFO の値段案を COO へ。CPO の v1 範囲案を GM へ。Apple のキーを Supabase に登録（社長）。10/2: 禁止語フィルター。Apple 連携の取り消し。アイコン PNG を CTO へ。CCO の窓口案（提出済みと議事録）。10/3: 承認リストを社長補佐へ。v1 機能と有料範囲を承認可能な状態に（CPO）。料金体系案を承認可能な状態に（CFO）。Mac を使う日の候補に 10/3 と 10/6。</t>
+          <t>実機確認は 10/4〜5（ヘルスケア）。ヘルスケアを「連携」と書くのは 10/5 まで待つ、と CMO。デモアカウントは手順とサンプルを CTO が用意し、本番作成は 10/6、社長承認後。</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2811,11 +2811,11 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>期限の一覧は org。AYG はそのうち購入画面と禁止語とトークン失効のコードが Draft PR にある、という状態。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="96" customHeight="1">
+          <t>未確認の一覧は AYG。日程は org。Apple token 失効を「やらなくてよい」とする README と、#29 および org の 10/2 は別行の食い違い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="81" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>スケジュール</t>
@@ -2823,17 +2823,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>10/4〜10/6 の期限</t>
+          <t>申請日</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>実機確認は未完、と法務 README。日付は書いていない。</t>
+          <t>日付の記載は法務 README には無い。TestFlight → 審査提出は、アイコンとスクショが揃ってから、とだけ書く。</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>10/4〜5: ヘルスケアの実機確認（CPO）。10/5: App Privacy の回答案（CTO）。アイコンとスクリーンショット（CPO 目標）。ヘルスケアを「連携」と書くのを待つ期限（CMO）。10/6: デモアカウントの本番作成（社長承認後）。ストア掲載文（CMO）。健康表現と価格未定時の書き方を社長へ（CMO）。Mac の日の候補。</t>
+          <t>COO: 2026-10-09 までに App Store 申請。計画は 10/7 申請、10/8-9 予備。CTO 目標: 10/7 に審査に通る状態で申請できるようにする。提出準備の議事録: 10/7 に審査で落ちない状態で提出する（期限 10/9）。承認事項のとりまとめ締めは 10/3。</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2849,29 +2849,29 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>日付は org のみ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="81" customHeight="1">
+          <t>日付は org-company のみ。10/7 と 10/9 は「計画の申請日」と「期限」として両方書いてある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="126" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ダウンロード数</t>
+          <t>10/1 前後の期限</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>購入画面の実装コミットは 2026-09-27 18:51〜18:59 JST に #27 ブランチへ入っている（#28/#29 に含まれる）。本番適用はしていない、と PR の積み方。</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>CMO 目標: 1か月目 1,000 人、半年 50,000 人、1年 500,000 人。2026-09-27 社長指示。現状欄は記録なし。獲得計画は確定 DL 0、数字は全て見込み。推奨は案 A（月 30 万円×3か月で単価と継続率を実測）。予算は未決定。1年目標を維持するか 90 日実測で見直すかは社長判断。</t>
+          <t>10/1: カロナビ+ 購入画面（CTO-CPO）。CFO の値段案を COO へ。CPO の v1 範囲案を GM へ。Apple のキーを Supabase に登録（社長）。10/2: 禁止語フィルター。Apple 連携の取り消し。アイコン PNG を CTO へ。CCO の窓口案（提出済みと議事録）。10/3: 承認リスト。窓口の議事録は「社長補佐へ」、COO 目標の現行文は「ゆりちゃんへ」。v1 機能と有料範囲を承認可能な状態に（CPO）。料金体系案を承認可能な状態に（CFO）。Mac を使う日の候補に 10/3 と 10/6。</t>
         </is>
       </c>
       <c r="E63" s="3" t="n"/>
@@ -2887,29 +2887,29 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>DL 目標は org-company のみ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="81" customHeight="1">
+          <t>期限の一覧は org。AYG はそのうち購入画面と禁止語とトークン失効のコードが Draft PR にある、という状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="96" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>利益</t>
+          <t>10/4〜10/6 の期限</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>実機確認は未完、と法務 README。日付は書いていない。</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>COO: 月の利益（カロナビ）は 3か月目 10 万円、半年 30 万円、1年 100 万円。GM の議事録上の見込み: 月 380 円、手数料 15% なら手取り約 323 円、費用を引く前でも約 310 人の有料会員。手数料が 15% かは未確認。上限を外すだけのカロナビ+ で届くかはデータが無く分からない、と GM。</t>
+          <t>10/4〜5: ヘルスケアの実機確認（CPO）。10/5: App Privacy の回答案（CTO）。アイコンとスクリーンショット（CPO 目標）。ヘルスケアを「連携」と書くのを待つ期限（CMO）。10/6: デモアカウントの本番作成（社長承認後）。ストア掲載文（CMO）。健康表現と価格未定時の書き方を社長へ（CMO）。Mac の日の候補。</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2925,29 +2925,29 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>利益目標は org-company のみ。達成人数の計算は見込みで、決定した料金ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="180" customHeight="1">
+          <t>日付は org のみ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="81" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>担当・体制</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>アプリ事業の役割</t>
+          <t>ダウンロード数</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>記載なし（組織図は無い）。法務 README の括弧書き担当: Google/Health の実機は Owner、不具合はエージェント、掲載テキストは Owner、見た目はエージェント、スクショは Owner（素材はデザイナー）、TestFlight は Owner。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>アプリ事業部の現在のプロダクトはカロナビ。GM-アプリ事業部、UIデザイナー(Ldr)、運用監視(Ldr)、獲得文章(Member)、ユーザー対応(Ldr)。役員目標: CPO は v1 と有料範囲（10/3）とアイコン・スクショ（10/5）。CTO は 10/7 に審査が通る状態。CFO は料金体系案（10/3）と経費の見える化。CMO は DL、獲得計画、掲載文（10/6）、価格決定後の LP。COO は申請進行と承認のとりまとめ。CCO 配下は問い合わせ。検査は作った人とは別の立場。本番反映とストア提出は社長の明示の承認までしない（CTO の役割）。現状欄は各役員とも記録なし。2026-09-27 の社長決定で秘書を廃止し、記録は34名。運用ルールは「社長に連絡できるのは社長補佐だけ」に更新された。</t>
+          <t>CMO 目標: 1か月目 1,000 人、半年 50,000 人、1年 500,000 人。2026-09-27 社長指示。現状欄は記録なし。獲得計画は確定 DL 0、数字は全て見込み。推奨は案 A（月 30 万円×3か月で単価と継続率を実測）。予算は未決定。1年目標を維持するか 90 日実測で見直すかは社長判断。</t>
         </is>
       </c>
       <c r="E65" s="3" t="n"/>
@@ -2963,29 +2963,29 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>体制は org-company。AYG は Owner とエージェントとデザイナー、という残タスクの担当だけ。秘書廃止はカロナビの機能仕様ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="96" customHeight="1">
+          <t>DL 目標は org-company のみ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="81" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
+          <t>利益</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>この日付の決定の写しは無い。9/27 の議事録が 380 円を「アプリに実装した値段」と呼ぶ。</t>
+          <t>COO: 月の利益（カロナビ）は 3か月目 10 万円、半年 30 万円、1年 100 万円。GM の議事録上の見込み: 月 380 円、手数料 15% なら手取り約 323 円、費用を引く前でも約 310 人の有料会員。手数料が 15% かは未確認。上限を外すだけのカロナビ+ で届くかはデータが無く分からない、と GM。</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -3001,29 +3001,29 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9/20 の決定文は AYG の法務 README。9/27 の org は値段を未決として扱っている（次の未決の行）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="156" customHeight="1">
+          <t>利益目標は org-company のみ。達成人数の計算は見込みで、決定した料金ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="180" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>担当・体制</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
+          <t>アプリ事業の役割</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
+          <t>記載なし（組織図は無い）。法務 README の括弧書き担当: Google/Health の実機は Owner、不具合はエージェント、掲載テキストは Owner、見た目はエージェント、スクショは Owner（素材はデザイナー）、TestFlight は Owner。</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>CPO: v1 に自由な Web 閲覧、いいね・コメント、広告は入れない。禁止語フィルターを入れる（範囲は CTO 案）。境界案に GM が賛成。購入画面の 3.1.2 と公開後指標を完成条件に足す。決まった値段にアプリと LP の両方を合わせる。窓口は案 A 前提で CCO が案を作る。提出準備の技術分担（マニフェスト、Apple 取り消し、デモアカウント、App Privacy、アイコン書き出し）を CTO が引き受ける。獲得計画は案 A を推奨として提出済み（確定ではない）。ストア文の書き方（目安、非医療、有料プラン明記、ダイエットはキーワード可）は CMO 議事録の決定事項。</t>
+          <t>アプリ事業部の現在のプロダクトはカロナビ。GM-アプリ事業部、UIデザイナー(Ldr)、運用監視(Ldr)、獲得文章(Member)、ユーザー対応(Ldr)。役員目標: CPO は v1 と有料範囲（10/3）とアイコン・スクショ（10/5）。CTO は 10/7 に審査が通る状態。CFO は料金体系案（10/3）と経費の見える化。CMO は DL、獲得計画、掲載文（10/6）、価格決定後の LP。COO は申請進行と承認のとりまとめ。CCO 配下は問い合わせ。検査は作った人とは別の立場。本番反映とストア提出は社長の明示の承認までしない（CTO の役割）。現状欄は各役員とも記録なし。2026-09-27 の社長決定で秘書を廃止し、記録は34名。その後、社長補佐の名前はゆりちゃんに変わった（役割は同じ、と更新履歴）。運用ルールは「社長に連絡できるのはゆりちゃん（社長補佐）だけ」。</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -3039,111 +3039,111 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>組織の決定は org-company。AYG はそれに対応する未マージのコードがある、という関係。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="141" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>値段は 380 か 480 か（CFO が 10/1 に案、決めるのは社長、それまで表記は触らない）。年齢区分を 18+ にするか（CPO 推奨、未決）。獲得予算（案 A か他か）。1年 DL 目標を維持するか 90 日で見直すか。Gmail を誰が読むか。返信の目安日数。Mac を使う日（10/3 と 10/6）。Apple キーの登録。アイコン3案から1つ（9/30）。デモアカウントの本番作成の承認（10/6）。機能の確定、料金体系、有料範囲の承認（COO、締め 10/3）。健康表現と価格未定時の書き方（10/6）。小規模事業者プログラムで手数料 15% かは未確認。</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>金額は未記載（断定しない、と書くだけ）。</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>食い違い</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>未決であることは org が明示。同時に AYG の公開 LP は 480 円を予定価格として出し、社内メモと ASC の記載は 380 円。CFO は決まるまで表記を変えるな、と言っているので、二つの数字が並んだまま。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="66" customHeight="1">
+          <t>体制は org-company。AYG は Owner とエージェントとデザイナー、という残タスクの担当だけ。秘書廃止はカロナビの機能仕様ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="96" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>この日付の決定の写しは無い。9/27 の議事録が 380 円を「アプリに実装した値段」と呼ぶ。</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>一部にしか記載なし</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>9/20 の決定文は AYG の法務 README。9/27 の org は値段を未決として扱っている（次の未決の行）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="156" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>未決事項</t>
+          <t>決定事項</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>食品データの出典・UI ルールブック・改名</t>
+          <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Open Food Facts をバーコードの取得元にする、と 01_Project。食品データベースの出典一覧や外食 DB の制約文書は、読んだブランチには無い。UI ルールブックというファイルも無い。カロリードへの改名の文字列は全コミットで 0 件。</t>
+          <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>食品出典の文書も UI ルールブックも改名の記録も無い。</t>
+          <t>CPO: v1 に自由な Web 閲覧、いいね・コメント、広告は入れない。禁止語フィルターを入れる（範囲は CTO 案）。境界案に GM が賛成。購入画面の 3.1.2 と公開後指標を完成条件に足す。決まった値段にアプリと LP の両方を合わせる。窓口は案 A 前提で CCO が案を作る。提出準備の技術分担（マニフェスト、Apple 取り消し、デモアカウント、App Privacy、アイコン書き出し）を CTO が引き受ける。獲得計画は案 A を推奨として提出済み（確定ではない）。ストア文の書き方（目安、非医療、有料プラン明記、ダイエットはキーワード可）は CMO 議事録の決定事項。</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>出典の文書は無い。名称はカロナビのまま。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>どこにも記載なし</t>
+          <t>一部にしか記載なし</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>読めた3リポジトリには、食品出典の専用文書、UI ルールブック、カロリードへの改名は無かった。company-os は未読なので、そこにあるかどうかは今回判定できない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+          <t>組織の決定は org-company。AYG はそれに対応する未マージのコードがある、という関係。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="141" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ブランチによって README が違う</t>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>main の README は Flutter の初期文だけ。web-preview と #29 は先頭にカロナビの説明と公開 URL。既定ブランチは main。</t>
+          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>値段は 380 か 480 か（CFO が 10/1 に案、決めるのは社長、それまで表記は触らない）。年齢区分を 18+ にするか（CPO 推奨、未決）。獲得予算（案 A か他か）。1年 DL 目標を維持するか 90 日で見直すか。Gmail を誰が読むか。返信の目安日数。Mac を使う日（10/3 と 10/6）。Apple キーの登録。アイコン3案から1つ（9/30）。デモアカウントの本番作成の承認（10/6）。機能の確定、料金体系、有料範囲の承認（COO、締め 10/3）。健康表現と価格未定時の書き方（10/6）。小規模事業者プログラムで手数料 15% かは未確認。</t>
         </is>
       </c>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>金額は未記載（断定しない、と書くだけ）。</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -3153,89 +3153,165 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>同じリポジトリの main とアプリ側ブランチで、最初に見える説明が違う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="81" customHeight="1">
+          <t>未決であることは org が明示。同時に AYG の公開 LP は 480 円を予定価格として出し、社内メモと ASC の記載は 380 円。CFO は決まるまで表記を変えるな、と言っているので、二つの数字が並んだまま。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="66" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ハンドブックの更新日と中身</t>
+          <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>docs/01_Project.md と docs/02_System_Architecture.md のヘッダは Last updated: 2026-07-22、Status は Version 1.1（承認済み）。git の最終更新は 2026-09-20。本文は 9 月の残タスク（docs/legal/README.md を参照）を含む。Decision Log の実ファイルは 0 バイトのまま。</t>
+          <t>Open Food Facts をバーコードの取得元にする、と 01_Project。食品データベースの出典一覧や外食 DB の制約文書は、読んだブランチには無い。UI ルールブックというファイルも無い。カロリードへの改名の文字列は全コミットで 0 件。</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>食品出典の文書も UI ルールブックも改名の記録も無い。</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
+          <t>出典の文書は無い。名称はカロナビのまま。</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>どこにも記載なし</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>読めた3リポジトリには、食品出典の専用文書、UI ルールブック、カロリードへの改名は無かった。company-os は未読なので、そこにあるかどうかは今回判定できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>main の README は Flutter の初期文だけ。web-preview と #29 は先頭にカロナビの説明と公開 URL。既定ブランチは main。</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>同じリポジトリの main とアプリ側ブランチで、最初に見える説明が違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="81" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>docs/01_Project.md と docs/02_System_Architecture.md のヘッダは Last updated: 2026-07-22、Status は Version 1.1（承認済み）。git の最終更新は 2026-09-20。本文は 9 月の残タスク（docs/legal/README.md を参照）を含む。Decision Log の実ファイルは 0 バイトのまま。</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>一部にしか記載なし</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>AYG の中で、文書の自己申告の日付と git の日付と、空の Decision Log が並んでいる。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="96" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74" ht="96" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>web-preview と #29 にあるデザイン資料は docs/design/README.md と 03_WORKOUT_INPUT.md。00_DESIGNER_BRIEF.md、01_INFORMATION_ARCHITECTURE.md、02_DELIVERABLES.md は PR #1 のブランチだけ。FIGMA の見た目コミットは PR #16 にあり、#29 には入っていない。デザイン README は実装の正を web-preview ブランチとしている（#29 ではない）。</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>UI デザイナーの役割説明のみ。納品物のファイルは無い。</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>一部にしか記載なし</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>デザインの正が web-preview と書かれたまま、新しいコードは #25〜#29 に積まれ、Figma 適用の2コミットは #16 に残っている。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H72">
-    <sortState ref="A1:H72">
+  <autoFilter ref="A1:H74">
+    <sortState ref="A1:H74">
       <sortCondition descending="0" ref="A2:A1000"/>
     </sortState>
   </autoFilter>
@@ -3259,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3315,7 +3391,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 19:42 JST 時点で、公開リポジトリ naruto-aii/AYG の全リモートブランチ20本と全PR（オープンは Draft 9本: #1 #11 #15 #16 #25 #26 #27 #28 #29）を git と GitHub API で読んだ。アプリコードの先端は Draft PR #29（cursor/apple-token-revoke-on-delete-eb80、48c4255、19:30 JST）。#28（bd3d3cb、19:00 JST）はその1つ下。main は LP と公開法務。web-preview はアプリ土台（9b4c961、09-25）。</t>
+          <t>2026-09-27 19:42 JST 時点で、公開リポジトリ naruto-aii/AYG の全リモートブランチ20本と全PR（オープンは Draft 9本: #1 #11 #15 #16 #25 #26 #27 #28 #29）を git と GitHub API で読んだ。アプリコードの先端は Draft PR #29（cursor/apple-token-revoke-on-delete-eb80、cdecdc7、19:51 JST）。#28（bd3d3cb、19:00 JST）はその下。#29 は 48c4255 の後に文書2件（0efb0de、cdecdc7）が乗っている。main は LP と公開法務。web-preview はアプリ土台（9b4c961、09-25）。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3851,32 +3927,32 @@
       </c>
     </row>
     <row r="20" ht="96" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>機能</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>運動記録・複数種目</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>01_Project: 手入力、運動履歴、消費カロリーの記録。デザイナー仕様 docs/design/03_WORKOUT_INPUT.md（増やさないカタログ）: ウォーキング、ランニング・ジョギング、自転車、水泳、筋トレ、バスケットボール、ヨガ・ストレッチ、家事・掃除、その他（手入力）。筋トレだけ任意で種目ごとのセット・回数・重量を複数。消費カロリーは実施時間から計算し、セット数では計算しない。追加消費は安静時を除いた net。歩きは「追加の運動／いつもの移動」。家事は生活活動係数に含まれる旨の注意。種類チップと検索は出さない。機能は凍結。</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/design/03_WORKOUT_INPUT.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/design/README.md</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/design/03_WORKOUT_INPUT.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/app-review/demo-account.md 、https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>03_WORKOUT_INPUT.md の git は 2026-09-21 08:35 JST（コミット 47c5c13 系の時刻は 09-20 23:35 UTC）。</t>
         </is>
@@ -3927,7 +4003,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Owner Decision: Apple Health / Health Connect と連携。利用時は Health データを計算に使う。非利用時は Activity Level。再同期。Web Preview では Health 非対応。Health の Workout を運動履歴へどう反映するかは Open Question（Q4）。entitlements に HealthKit。用途文は目標計算だけ、広告・マーケティングには使わない。法務 README: 実機で Google ログインと Health を通すのが残タスク。初回にやらなくてよい項目に「Health Workout の運動反映」がある。</t>
+          <t>Owner Decision: Apple Health / Health Connect と連携。利用時は Health データを計算に使う。非利用時は Activity Level。再同期。Web Preview では Health 非対応。Health の Workout を運動履歴へどう反映するかは Open Question（Q4）。entitlements に HealthKit。#29 先端（cdecdc7）の用途文は「読み取り、カロリー目標の計算と記録の表示に使う。広告やマーケティングには使わない」。同じ先端の demo-account.md と app-privacy-draft.md は、読むのは生年月日・性別・身長・体重・アクティブエネルギー・ワークアウトだけで、歩数は読まない、書き込み権限は無い、と書く。法務 README: 実機で Google ログインと Health を通すのが残タスク。初回にやらなくてよい項目に「Health Workout の運動反映」がある。</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4438,7 +4514,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="96" customHeight="1">
+    <row r="39" ht="111" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>プライバシー</t>
@@ -4451,12 +4527,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>#28/#29 の ios/Runner/PrivacyInfo.xcprivacy。NSPrivacyTracking は false。追跡ドメインなし。Required Reason API: UserDefaults CA92.1、File timestamp C617.1 と 0A2A.1、System boot time 35F9.1、Disk space 7D9E.1。収集データ: メール、ユーザー ID（機能と Analytics）、Health（機能）、Product Interaction（Analytics）。main と web-preview にこのファイルは無い。PR #28 本文は、共有 UserDefaults の用途をサブスク期限、日次の公開食品検索回数、最終ログインユーザー ID と説明。</t>
+          <t>#28 の ios/Runner/PrivacyInfo.xcprivacy。NSPrivacyTracking は false。追跡ドメインなし。Required Reason API: UserDefaults CA92.1、File timestamp C617.1 と 0A2A.1、System boot time 35F9.1、Disk space 7D9E.1。#28 時点の収集データ: メール、ユーザー ID（機能と Analytics）、Health（機能）、Product Interaction（Analytics）。#29 先端 cdecdc7 は、これに Fitness、Purchase History、Other User Content、Other Data Types を足している。main と web-preview にこのファイルは無い。PR #28 本文は、共有 UserDefaults の用途をサブスク期限、日次の公開食品検索回数、最終ログインユーザー ID と説明。</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/ios-privacy-iphone-only-eb80/ios/Runner/PrivacyInfo.xcprivacy 、https://github.com/naruto-aii/AYG/pull/28</t>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/ios/Runner/PrivacyInfo.xcprivacy 、https://github.com/naruto-aii/AYG/pull/28 、https://github.com/naruto-aii/AYG/pull/29</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4466,11 +4542,11 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>コミット bd3d3cb は 19:00 JST。旧オブジェクト 70f0bb0 も同タイトル。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="126" customHeight="1">
+          <t>#28 の bd3d3cb は 19:00 JST。収集種別の追加は #29 の cdecdc7（19:51 JST）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="141" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>プライバシー</t>
@@ -4483,7 +4559,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>#29 の legal/privacy.html（ページ上の最終更新日 2026-09-27）: アカウント識別子（Google または Apple、メール）、基本情報と目標、食事・アルコール・運動・体重・保存食品・公開食品、Health または Health Connect、バーコード、Good/Bad・通報・ブロック、問い合わせメール、ストアの購入状態（カード番号は取らない）、利用状況（上限到達と有料切替をユーザー ID に紐づけ）。広告識別子は取らない。Health は広告・マーケティングに使わない。第三者に Google LLC（Google ログイン、Health Connect）。アプリ内課金の第三者としての Google の行は、main の公開版にはあり、#29 版では外している。利用状況の項目は #29 版にあり、公開中の main 版には無い。</t>
+          <t>#29 先端 cdecdc7 の legal/privacy.html: 最終更新日の欄は「【公表日：社長確認後に記入】」。取得は、Google または Apple の識別子、基本情報と目標、食事・アルコール・運動・体重・保存食品・公開食品、Apple Health の読み取り（Health Connect の行は外した）、バーコード、Good/Bad・通報・ブロック、問い合わせ、購入状態（購入の有無と期限だけ。カード番号は取らない）、利用状況（上限に初めて達した日時とカロナビ+へ切り替えた日時。食事内容やレシートは含まない）、Sign in with Apple の更新用トークン（削除時の連携解除のため、暗号化してサーバーに保存）。委託先の国名、Open Food Facts の運営主体と所在国、バックアップ保持日数、開示手数料は「社長確認後に記入」のプレースホルダ。公開中の main 版は Health Connect と Google Play 課金を含み、利用状況と Apple トークンの行は無い。</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4498,39 +4574,39 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>公開版の git は main の docs/legal。アプリ同梱版の git は 2026-09-27 18:59 JST。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="96" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>法務</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>法務ページの置き場（2系統）</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>公開中は main の docs/legal/ を https://naruto-aii.github.io/AYG/legal/ に出す（目次、privacy、terms、tokushoho、support、account-deletion）。アプリ同梱は #29 の legal/ 以下の同じ6ファイルで、アプリ内は全画面表示。外部リンクは Safari、と org が CTO 確認として記録。01_Project: 公開 HTML の原稿は legal/。弁護士確認は未実施、と法務 README。参照した公開書類: あすけん、カロミル、FiNC、消費者庁・特商法11条、個人情報保護法。</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/main/.github/workflows/publish-pages.yml 、https://github.com/naruto-aii/AYG/blob/main/docs/legal/ 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/ 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
+          <t>公開版は main。アプリ同梱版の先端は 2026-09-27 19:51 JST の cdecdc7。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="171" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プライバシー</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>#29 先端の docs/app-review/app-privacy-draft.md。案であり、App Store Connect にはまだ入力していない。弁護士確認はしていない。トラッキングしない。収集する、と書くもの: User ID、Product Interaction（上限に初めて達した日時。Analytics）、Purchase History（有料へ切り替えた日時。レシートや取引 ID は表に入れない）、Email、Health（歩数はリストに無い。ワークアウト行は端末内の Isar だけで収集としては宣言しない）、Fitness（サーバーに残るアクティブエネルギーと運動記録）、Other User Content（保存食品、公開食品、テンプレート、目標、評価、通報、ブロック。写真は保存しない）、Other Data Types（Sign in with Apple の refresh token。保存するので申告する）。収集しない: 位置、連絡先、閲覧履歴、カード番号、クラッシュ、広告 ID、検索履歴、氏名（fullName はスコープにあるが保存しない）。Google の Health Connect は iPhone 提出では使わない、と書く。Supabase の保存先リージョンはリポジトリからは特定できない、と書く。</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/app-review/app-privacy-draft.md 、https://github.com/naruto-aii/AYG/pull/29</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27 に公開 URL の特商法を取得し、Google Play の行があることを確認した（main と一致）。</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>0efb0de で下書き、cdecdc7 でプレースホルダ付きの反映、とコミットメッセージ。</t>
         </is>
       </c>
     </row>
@@ -4542,239 +4618,243 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
+          <t>法務ページの置き場（2系統）</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>公開中は main の docs/legal/ を https://naruto-aii.github.io/AYG/legal/ に出す（目次、privacy、terms、tokushoho、support、account-deletion）。アプリ同梱は #29 の legal/ 以下の同じ6ファイルで、アプリ内は全画面表示。外部リンクは Safari、と org が CTO 確認として記録。01_Project: 公開 HTML の原稿は legal/。弁護士確認は未実施、と法務 README。参照した公開書類: あすけん、カロミル、FiNC、消費者庁・特商法11条、個人情報保護法。</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/main/.github/workflows/publish-pages.yml 、https://github.com/naruto-aii/AYG/blob/main/docs/legal/ 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/ 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 に公開 URL の特商法を取得し、Google Play の行があることを確認した（main と一致）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="96" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>法務</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
           <t>利用規約の記載</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>法務 README が埋めた項目: 適用、定義、非医療、アカウント、未成年、課金・定期購入の解約、公開食品の利用許諾、禁止、知財、退会、非保証、損害賠償の上限、反社、地位譲渡、分離可能性、変更、準拠法。#29 の terms: 運営は麹池成、ストアは現在 App Store、日本法、東京地方裁判所を第一審の専属的合意管轄。公開食品は削除後も残り、作成者欄は「削除済みユーザー」。main の公開 terms はストアを App Store または Google Play とし、「削除済みユーザー」の文は #29 との diff で追加側（公開版にはその文が無い）。</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/terms.html 、https://github.com/naruto-aii/AYG/blob/main/docs/legal/terms.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>terms のページ上の最終更新日はどちらも 2026-09-20。差分は日付行以外にもある。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="126" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="126" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>法務</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>特定商取引法の記載</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>共通: 販売業者 麹池成、住所は東京都で請求と本人確認のうえ開示、電話も請求開示、メール calonavi.ayg.support@gmail.com、送料なし、通信料は利用者、提供は決済後すぐ、申込期限なし、返品は原則不可で返金はストア、定期購入の解約はストア（アプリ削除・ログアウト・アカウント削除では止まらない）。違い: 公開中（main、ページ上 2026-09-20）は支払方法が App Store または Google Play、動作環境は iOS または Android、販売価格は「各購入画面に税込で表示」。未マージ（#29、ページ上 2026-09-27）は支払方法が App Store、動作環境は App Store の iOS、販売価格は「App Store の購入画面に表示される価格。このページでは金額を定めません」。380 円も 480 円も特商法 HTML には書いていない。</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/main/docs/legal/tokushoho.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/tokushoho.html 、公開 https://naruto-aii.github.io/AYG/legal/tokushoho.html</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F43" s="4" t="n"/>
-    </row>
-    <row r="44" ht="81" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>法務</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>アカウント削除の法務文</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>アプリ内: ログイン、設定、アカウント削除、案内を確認して実行。メール: ログインに使ったアドレスから件名「アカウント削除」。消えるもの: 食事・運動・体重などの個人記録、非公開の保存食品、食事テンプレート、プロフィール、目標、Health の個人向けデータ。残るもの: 公開食品。#29 版は作成者欄を「削除済みユーザー」。公開中の main 版は氏名やメールを載せない、までで、その「削除済みユーザー」の文は diff 上 #29 側だけ。課金は自動では止まらない。</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/account-deletion.html 、https://github.com/naruto-aii/AYG/blob/main/docs/legal/account-deletion.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>両 HTML のページ上の最終更新日は 2026-09-20。</t>
-        </is>
-      </c>
+      <c r="F44" s="4" t="n"/>
     </row>
     <row r="45" ht="96" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>法務</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>アカウント削除の法務文</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>アプリ内: ログイン、設定、アカウント削除、案内を確認して実行。メール: ログインに使ったアドレスから件名「アカウント削除」。消えるもの: 食事・運動・体重などの個人記録、非公開の保存食品、食事テンプレート、プロフィール、目標、Health の個人向けデータ。#29 先端は、アカウント情報（メールアドレス等）と利用状況の記録、Sign in with Apple の連携解除を消えるものに足している。残るもの: 公開食品。#29 版は作成者欄を「削除済みユーザー」。公開中の main 版にはその文が無い。課金は自動では止まらない。</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/account-deletion.html 、https://github.com/naruto-aii/AYG/blob/main/docs/legal/account-deletion.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>両 HTML のページ上の最終更新日は 2026-09-20。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>掲載文・キーワード</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>草案は PR #1 の docs/store/APP_STORE_LISTING.md のみ（#28/#29 には無い）。プロモーション文、説明、What's New、キーワード草案（カロリー,食事,運動,体重,ダイエット,PFC,タンパク質,減量,増量,ヘルスケア,記録,エネルギー）。書いてはいけないこと: 店名の AYG、治療・診断、課金や広告があるかのような表現、ゲスト・英語・Android 先行、サポート URL を確定したかのような記述、法務文面を確定と書くこと。法務 README の残タスク: 掲載テキスト（URL、年齢、Privacy Nutrition Labels、審査メモ）。スクショとアイコンは空のまま、と README。</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/designer-brief-08a9/docs/store/APP_STORE_LISTING.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>掲載文ファイルの git は 2026-09-20。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="126" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47" ht="126" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>スクリーンショット・アイコン</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>iOS の AppIcon.appiconset に 1024 を含む PNG がある。assets/brand/app_icon_placeholder.svg がある。法務 README: スクリーンショットとアイコンは空のまま先にテキストだけ入れる。見た目・アイコン・スクショ・TestFlight はデザイン後。PR #1 にスクショ用コピー5行（今日あと何kcal、食事は打つ・撮る・選ぶ、運動、体重、根拠）。ストア用スクショ画像のセットはリポジトリに無い。</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/ios/Runner/Assets.xcassets/AppIcon.appiconset/ 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/assets/brand/app_icon_placeholder.svg 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/designer-brief-08a9/docs/store/APP_STORE_LISTING.md</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="96" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="F47" s="3" t="n"/>
+    </row>
+    <row r="48" ht="141" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>審査用デモアカウント</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>#29 先端の docs/app-review/demo-account.md。App Review 用。本番 Supabase で作り、パスワードと Sandbox のパスワードと Apple の秘密鍵はファイルに書かない。ログインは Sign in with Apple と Google のみ。メールとパスワードのログインは無い。審査用の共有アカウントは Google で作る。ストア名は「カロナビ - 食事と運動」。Bundle ID は com.narutoaii.ayg。提出ビルドは iPhone のみ。サンプルは、今日の食事とアルコール、ウォーキング 30 分、体重、バーコード（画像は保存しない）、Health の読み取り、カロナビ+ の Sandbox 購入と復元。価格はこの文書では固定しない。無料枠は検索 5 回/日、食事テンプレート 3、運動テンプレート 3。上限に達した回数そのものはサーバーに保存せず、初めて達した日時と有料へ切り替えた日時だけ。審査中はデモアカウントを削除しない。main と web-preview にこのファイルは無い。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/app-review/demo-account.md 、https://github.com/naruto-aii/AYG/pull/29</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>コミット cdecdc7 は 19:51 JST。ファイル追加は 0efb0de（19:37 JST）から。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="96" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>公開 URL とページの数</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>README（web-preview/#29）: 公開 Preview は https://naruto-aii.github.io/AYG/ 、ランディングページは https://naruto-aii.github.io/AYG/lp/ 。main の docs/index.html がその LP。sitemap は /lp/ と /legal/。workflow は Pages ルートを web-preview、LP を /lp/、法務を /legal/。</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/README.md 、https://github.com/naruto-aii/AYG/blob/main/docs/index.html 、https://github.com/naruto-aii/AYG/blob/main/docs/sitemap.xml 、https://github.com/naruto-aii/AYG/blob/main/.github/workflows/publish-pages.yml 、https://naruto-aii.github.io/AYG/lp/</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>main の README は Flutter の初期文のままで、LP の URL を書いていない。URL を書く README は web-preview と #29。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="81" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>「App Storeで公開中」の表記</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>main の docs/index.html: 「App Storeで公開中（リンク準備中）」。FAQ「いつ使えますか？」の答えは「App Storeで公開しています。」法務 README の残タスクは TestFlight の前（アイコンとスクショが揃ってから出す）。01_Project は App Store での公開を予定、と書く。</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/main/docs/index.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n"/>
-    </row>
-    <row r="49" ht="51" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>価格の書き方</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>AYG の /lp/: 予定価格（作業ベース）月額 480 円／年額 4,800 円。最終は App Store の購入画面が正。無料の目安は検索 5 回/日、食事テンプレート 3、運動テンプレート 3。カロナビ+ は上限を拡大、と書く。</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>ページ内の更新日は 2026-09-24。</t>
         </is>
       </c>
     </row>
@@ -4786,181 +4866,177 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>「App Storeで公開中」の表記</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>main の docs/index.html: 「App Storeで公開中（リンク準備中）」。FAQ「いつ使えますか？」の答えは「App Storeで公開しています。」法務 README の残タスクは TestFlight の前（アイコンとスクショが揃ってから出す）。01_Project は App Store での公開を予定、と書く。</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/main/docs/index.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="51" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>価格の書き方</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>AYG の /lp/: 予定価格（作業ベース）月額 480 円／年額 4,800 円。最終は App Store の購入画面が正。無料の目安は検索 5 回/日、食事テンプレート 3、運動テンプレート 3。カロナビ+ は上限を拡大、と書く。</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>ページ内の更新日は 2026-09-24。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="81" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>機能説明の差（繰り越し・写真解析）</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>main の LP: 見る・入れる・戻す。アルコールは別記録。運動は MET または kcal 直接入力。体重の一覧・追加・編集・削除。ログインは Google または Apple。向いていない人に、写真自動解析だけが欲しい方（現状の主機能ではない）、ゲストのまま使いたい方。超過の翌日繰り越しが無い、とはこの LP は書いていない（「戻す — 食べ過ぎた日も超過を事実として見て、次の日の感覚を残す」）。</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>cursor/lp-v2-landing-c48e は main の祖先（PR #22 マージ済み）で、main より新しいコミットは無い。いまの LP は #22 の後の #20/#21/#24 を含む main。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="81" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="53" ht="81" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>サポート</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>窓口のメールと URL</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>calonavi.ayg.support@gmail.com。公開 URL https://naruto-aii.github.io/AYG/legal/support.html 。受付は順次、数日以内を目安。アカウントの依頼はログインに使っているメールから。法務 README: 新しい仕組みは作らない。その Gmail を見られればよい。</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/legal/support.html 、https://github.com/naruto-aii/AYG/blob/main/docs/legal/support.html 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>support.html は main と #29 で、今回の diff では本文の差を価格や Google Play の行としては出していない（中身はほぼ同じ）。ページ上の最終更新日は 2026-09-20。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="51" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54" ht="51" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>公開URL</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>いま開く URL</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>https://naruto-aii.github.io/AYG/ （web-preview 由来の Web プレビュー。2026-09-27 に HTTP 200）。https://naruto-aii.github.io/AYG/lp/ （main の LP。200）。https://naruto-aii.github.io/AYG/legal/ 以下（main の法務。特商法は 200 で Google Play の行あり）。</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/main/.github/workflows/publish-pages.yml 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/README.md</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="81" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="81" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>main と web-preview の分け方</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>既定ブランチは main。publish-pages.yml: アプリ本体は main に merge しない。Pages のルートは常に web-preview。main の README は Flutter の初期文。web-preview と #29 の README は先頭がカロナビの説明で、その下に Flutter 初期文が残る。main に docs/01_Project.md は無い。web-preview の先端は 9b4c961（2026-09-25、PR #23 マージ）。main の先端は c6d5c6e（2026-09-25、PR #24 マージ）。</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/main/.github/workflows/publish-pages.yml 、https://github.com/naruto-aii/AYG/blob/main/README.md 、https://github.com/naruto-aii/AYG/blob/web-preview/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/README.md</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F53" s="3" t="n"/>
-    </row>
-    <row r="54" ht="96" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>すべて Draft、未マージ。#25 integrate-pr11-web-preview-eb80 → web-preview（947a8b1）。#26 public-food-banned-names-eb80 → #25 のブランチ（3035c58）。#27 calonavi-plus-paywall-eb80 → #26 のブランチ（c03dd07）。#28 ios-privacy-iphone-only-eb80 → #27 のブランチ（bd3d3cb）。#29 apple-token-revoke-on-delete-eb80 → #28 のブランチ（48c4255）。2026-09-27 19:42 JST 時点で #25 と #26 の先端は #28 の祖先（#28 に入っていないコミットは 0）。#29 が #28 の1コミット先。</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/pull/25 https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/28 https://github.com/naruto-aii/AYG/pull/29</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>PR の updatedAt は #29 が 10:33 UTC、#25〜#28 が 10:03〜10:05 UTC。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="126" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>旧先端 70f0bb0（2026-09-27 09:27 UTC、fix: add the iOS privacy manifest and ship iPhone-only）から見て、#26 ブランチ側にだけあったコミットは次の4つ。947a8b1（#25、18:39 JST）fix: show Japanese errors and note that revert keeps applied columns。0b59956（#26、18:43 JST）feat: reject banned words in public food names。94ab79c（#26、18:43 JST）fix: check every public food text field after NFKC folding。3035c58（#26、18:50 JST）fix: accept ordinary foods and compose halfwidth voiced marks。現在の #28（bd3d3cb、19:00 JST）は rebase 後で、この4つを祖先に含む。70f0bb0 側にだけあったコミット（70f0bb0、e81c320、11619dc、ab95e99、931019c）は現在の #28 の歴史には無い。</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>git log 70f0bb0c3bd640b6a3f1578ff1d1b400050597c5 と bd3d3cb と origin/cursor/public-food-banned-names-eb80</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>70f0bb0 は git fetch でオブジェクトを取得した。ブランチ名としては残っていない。</t>
-        </is>
-      </c>
+      <c r="F55" s="3" t="n"/>
     </row>
     <row r="56" ht="111" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -4970,161 +5046,169 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
+          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>すべて Draft、未マージ。#25 integrate-pr11-web-preview-eb80 → web-preview（947a8b1）。#26 public-food-banned-names-eb80 → #25 のブランチ（3035c58）。#27 calonavi-plus-paywall-eb80 → #26 のブランチ（c03dd07）。#28 ios-privacy-iphone-only-eb80 → #27 のブランチ（bd3d3cb）。#29 apple-token-revoke-on-delete-eb80 → #28 のブランチ。先端は cdecdc7（19:51 JST）。その下は 0efb0de（19:37 JST）と 48c4255（19:30 JST）。2026-09-27 19:51 JST 時点で #25 と #26 の先端は #28 の祖先（#28 に入っていないコミットは 0）。#29 は #28 より3コミット先。</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/pull/25 https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/28 https://github.com/naruto-aii/AYG/pull/29</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>PR の updatedAt は #29 が 10:33 UTC、#25〜#28 が 10:03〜10:05 UTC。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="126" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>ブランチ・PR</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>旧先端 70f0bb0（2026-09-27 09:27 UTC、fix: add the iOS privacy manifest and ship iPhone-only）から見て、#26 ブランチ側にだけあったコミットは次の4つ。947a8b1（#25、18:39 JST）fix: show Japanese errors and note that revert keeps applied columns。0b59956（#26、18:43 JST）feat: reject banned words in public food names。94ab79c（#26、18:43 JST）fix: check every public food text field after NFKC folding。3035c58（#26、18:50 JST）fix: accept ordinary foods and compose halfwidth voiced marks。現在の #28（bd3d3cb、19:00 JST）は rebase 後で、この4つを祖先に含む。70f0bb0 側にだけあったコミット（70f0bb0、e81c320、11619dc、ab95e99、931019c）は現在の #28 の歴史には無い。</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>git log 70f0bb0c3bd640b6a3f1578ff1d1b400050597c5 と bd3d3cb と origin/cursor/public-food-banned-names-eb80</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>70f0bb0 は git fetch でオブジェクトを取得した。ブランチ名としては残っていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="111" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ブランチ・PR</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>古い Draft PR（#1 #11 #15 #16）</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>#1 designer-brief-08a9 → main。デザイナー要件、ストア掲載文草案、法務 Markdown。main に無いコミットが5。更新 09-20。#11 legal-pages-and-public-food-ab66 → web-preview。アカウント削除、カロナビ+、Apple ログイン。先端 5f6e87a は #25 の祖先（#25 に含まれ、#11 だけにあるコミットは 0）。オープンのまま。#15 setup-flutter-cloud-env-96c6 → #11 のブランチ。Isar ネイティブ lib の ignore 等、#29 に無いコミットが3（2ceaec2、1783bf5、373da7c）。#16 figma-visual-design-ab66 → web-preview。#29 に無いコミットが2（910abf3 feat: apply delivered Figma visual system、ef563e6 fix: match Figma inspect values）。</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/pull/1 https://github.com/naruto-aii/AYG/pull/11 https://github.com/naruto-aii/AYG/pull/15 https://github.com/naruto-aii/AYG/pull/16</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>#16 の最終コミットは 2026-09-21 11:56 JST。#15 は 2026-09-21 11:14 JST。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="81" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="59" ht="81" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>マージ済みで先端に差が無いブランチ</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>web-preview の祖先: feature/v1.1-food-master-supabase、workout-input-redesign、workout-input-simplify、workout-design-brief（PR #12 #13 #14 はマージ済み）。main の祖先: lp-v2-landing-c48e（PR #22）、価格文言の PR #20 #21、LP 公開の #17〜#19、split-lp の #24。pages-keep-web-root は web-preview に #23 でマージ済み。fix-web-preview-deploy と main-web-preview-workflow は 09-19 のデプロイ修正ブランチで、オープン PR は無い。</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/pulls</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n"/>
-    </row>
-    <row r="58" ht="66" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="F59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="66" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>開発状況</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>法務 README が「済んでいる」とするもの</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>法務 HTML とアプリ内全画面、Sign in with Apple（Developer Key、Supabase Apple Enabled、アプリ配線。Web プレビューでは使えない）、アカウント削除 UI と本番 RPC、カロナビ+ のアプリ側と ASC 商品、ストアのアプリ枠（名前はカロナビ - 食事と運動）、公開食品の作成者欄「削除済みユーザー」、通報・作成者ブロック。機能は凍結済み。デザイナーへ見た目を依頼中。</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="126" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="F60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="126" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>開発状況</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>実機未確認と残タスク</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>法務 README: 実機の機能確認は未完。仮デザインのまま。購入含む。残りの実機確認: Apple ログイン、キーボード、筋トレ複数種目、バーコードカメラ、アカウント削除、公開食品の「削除済みユーザー」、検索5回とテンプレ3件、カロナビ+ の購入と復元（Sandbox）。Google ログインと Health を実機で通す手順は docs/setup/ios_google_health.md（Bundle ID com.narutoaii.ayg、Redirect com.narutoaii.ayg://login-callback、HealthKit capability）。デザイン後: 見た目、アイコン、スクショ、見た目込みの実機、TestFlight → 審査。初回にやらなくてよい: Google Play、法人名義、体重タブの機能追加、Health Workout の運動反映、写真解析、Apple token 失効、レシートのサーバ検証。</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/setup/ios_google_health.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n"/>
-    </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>申請日</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>日付の記載は法務 README には無い。TestFlight → 審査提出は、アイコンとスクショが揃ってから、とだけ書く。</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>10/1 前後の期限</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>購入画面の実装コミットは 2026-09-27 18:51〜18:59 JST に #27 ブランチへ入っている（#28/#29 に含まれる）。本番適用はしていない、と PR の積み方。</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/29</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -5142,304 +5226,360 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
+          <t>申請日</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>日付の記載は法務 README には無い。TestFlight → 審査提出は、アイコンとスクショが揃ってから、とだけ書く。</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n"/>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>10/1 前後の期限</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>購入画面の実装コミットは 2026-09-27 18:51〜18:59 JST に #27 ブランチへ入っている（#28/#29 に含まれる）。本番適用はしていない、と PR の積み方。</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/29</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n"/>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/4〜10/6 の期限</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>実機確認は未完、と法務 README。日付は書いていない。</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>目標</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>ダウンロード数</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>目標</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>利益</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="51" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>担当・体制</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>アプリ事業の役割</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>記載なし（組織図は無い）。法務 README の括弧書き担当: Google/Health の実機は Owner、不具合はエージェント、掲載テキストは Owner、見た目はエージェント、スクショは Owner（素材はデザイナー）、TestFlight は Owner。</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n"/>
-    </row>
-    <row r="66" ht="66" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>決定事項</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>見出しは「課金（2026-09-20 決定）」。ファイルの git 更新は 2026-09-27。</t>
-        </is>
-      </c>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
     </row>
     <row r="67" ht="51" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>担当・体制</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>アプリ事業の役割</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>記載なし（組織図は無い）。法務 README の括弧書き担当: Google/Health の実機は Owner、不具合はエージェント、掲載テキストは Owner、見た目はエージェント、スクショは Owner（素材はデザイナー）、TestFlight は Owner。</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n"/>
+    </row>
+    <row r="68" ht="66" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/28 https://github.com/naruto-aii/AYG/pull/29</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n"/>
-    </row>
-    <row r="68" ht="81" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>見出しは「課金（2026-09-20 決定）」。ファイルの git 更新は 2026-09-27。</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="51" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27 の議事録で決まったこと</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/28 https://github.com/naruto-aii/AYG/pull/29</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n"/>
+    </row>
+    <row r="70" ht="81" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n"/>
+    </row>
+    <row r="71" ht="51" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>未決事項</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Open Food Facts をバーコードの取得元にする、と 01_Project。食品データベースの出典一覧や外食 DB の制約文書は、読んだブランチには無い。UI ルールブックというファイルも無い。カロリードへの改名の文字列は全コミットで 0 件。</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>git log -S カロリード と Calolead は AYG・org-company・lp で 0 件。</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="51" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="72" ht="51" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>ブランチによって README が違う</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>main の README は Flutter の初期文だけ。web-preview と #29 は先頭にカロナビの説明と公開 URL。既定ブランチは main。</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/main/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/README.md</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>main の README の git は 2026-07-21。アプリ側 README の git は 2026-09-25。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="96" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="73" ht="96" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>ハンドブックの更新日と中身</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>docs/01_Project.md と docs/02_System_Architecture.md のヘッダは Last updated: 2026-07-22、Status は Version 1.1（承認済み）。git の最終更新は 2026-09-20。本文は 9 月の残タスク（docs/legal/README.md を参照）を含む。Decision Log の実ファイルは 0 バイトのまま。</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/02_System_Architecture.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/05_DECISION_LOG.md</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F71" s="3" t="n"/>
-    </row>
-    <row r="72" ht="66" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="F73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="66" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>web-preview と #29 にあるデザイン資料は docs/design/README.md と 03_WORKOUT_INPUT.md。00_DESIGNER_BRIEF.md、01_INFORMATION_ARCHITECTURE.md、02_DELIVERABLES.md は PR #1 のブランチだけ。FIGMA の見た目コミットは PR #16 にあり、#29 には入っていない。デザイン README は実装の正を web-preview ブランチとしている（#29 ではない）。</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/design/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/designer-brief-08a9/docs/design/00_DESIGNER_BRIEF.md 、https://github.com/naruto-aii/AYG/pull/16</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5460,7 +5600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5503,7 +5643,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
+    <row r="2" ht="66" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>調査範囲</t>
@@ -5516,7 +5656,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 時点の main 先端は 9f6a176（PR #7 の Note 目標のあと、社長決定で秘書を廃止）。オープンPRは0。カロナビの議事録5本は main にある。リモートブランチは main 以外5本で、いずれも main より先行コミット0（すべて main の祖先）。</t>
+          <t>2026-09-27 時点の main 先端は 0a779bc（秘書廃止のあと、社長補佐の名前をゆりちゃんに変更。役割は同じ、と更新履歴）。オープンPRは0。カロナビの議事録5本は main にある。議事録の文面は「社長補佐」のまま。リモートブランチは main 以外5本で、いずれも main より先行コミット0（すべて main の祖先）。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5976,32 +6116,32 @@
       <c r="F19" s="3" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>機能</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>運動記録・複数種目</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>運動の記録は無料、と境界案。種目一覧は書いていない。</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -6532,56 +6672,64 @@
       <c r="F40" s="4" t="n"/>
     </row>
     <row r="41" ht="66" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プライバシー</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案は 10/5 までに CTO が作る。利用データ（利用者に紐づく）が加わる見込み、と CTO-CPO 議事録。</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/技術本部（CTO）/2026-09-27_禁止語フィルターと購入画面.md</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="66" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>法務</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>法務ページの置き場（2系統）</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>サポート URL は naruto-aii.github.io/AYG/legal/ を使う案 A。場所を変えない。</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>要点: Webビューは使っていない。法務ページはアプリに同梱し、外部リンクは Safari。</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>法務</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>利用規約の記載</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>記載なし（条文の写しは無い）。</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -6591,19 +6739,19 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>特定商取引法の記載</t>
+          <t>利用規約の記載</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>特商法の条文写しは無い。値段は社長未決。</t>
+          <t>記載なし（条文の写しは無い）。</t>
         </is>
       </c>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
     </row>
-    <row r="44" ht="36" customHeight="1">
+    <row r="44" ht="22" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>法務</t>
@@ -6611,137 +6759,129 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
+          <t>特定商取引法の記載</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>特商法の条文写しは無い。値段は社長未決。</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>法務</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>アカウント削除の法務文</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>削除後の公開食品は残し、作成者欄は「削除済みユーザー」、と法務 README の決定を org は直接は書いていない。CPO はアカウント削除を無料機能に数えている。</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="66" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="F45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="66" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>掲載文・キーワード</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>CMO 議事録の決定: 数値は必ず「目安」、医療機器でない旨、効果・病名・根拠のない実績は使わない、有料プランの存在は明記、「ダイエット」はキーワード欄で可。ヘルスケアは 10/5 まで「連携」と書かない。4+ は使わない。ストア掲載文の期限は CMO 目標で 10/6。健康表現の最終線引きと、価格未定時の料金の書き方は 10/6 の掲載文完成時に社長へ。</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md 、https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n"/>
-    </row>
-    <row r="46" ht="81" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="F46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="81" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>スクリーンショット・アイコン</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>アイコン3案から1つを社長が選ぶ（9/30）。1024×1024 の PNG、透過なしを 10/2 までに CTO へ。アイコンとスクリーンショットは CPO 目標で 10/5 まで。3案の画像ファイルは org-company には無い。</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/CPO/CPO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="51" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>公開 URL とページの数</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>LP の URL を議事録は一つに決めていない。CPO は「LP に書いた値段」と言う。CMO 目標に「価格決定後の LP 修正」。</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="F47" s="3" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>審査用デモアカウント</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>提出準備: 手順とサンプルデータは CTO が用意。本番での作成は 10/6、社長の承認後。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>「App Storeで公開中」の表記</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>COO 目標: 2026-10-09 までに App Store 申請（計画は 10/7 申請、10/8-9 予備）。申請はこれから、という日程。</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/org-company/blob/main/COO/COO.md</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n"/>
+      <c r="F48" s="2" t="n"/>
     </row>
     <row r="49" ht="51" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -6751,12 +6891,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>価格の書き方</t>
+          <t>公開 URL とページの数</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>CMO の役割: 値段が決まっていなければ未定と書く。CFO: 決まるまでアプリと LP の表記は触らない。</t>
+          <t>LP の URL を議事録は一つに決めていない。CPO は「LP に書いた値段」と言う。CMO 目標に「価格決定後の LP 修正」。</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -6779,135 +6919,139 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>「App Storeで公開中」の表記</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>COO 目標: 2026-10-09 までに App Store 申請（計画は 10/7 申請、10/8-9 予備）。申請はこれから、という日程。</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/COO/COO.md</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="51" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>価格の書き方</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>CMO の役割: 値段が決まっていなければ未定と書く。CFO: 決まるまでアプリと LP の表記は触らない。</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n"/>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>機能説明の差（繰り越し・写真解析）</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="66" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+    </row>
+    <row r="53" ht="66" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>サポート</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>窓口のメールと URL</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>案 A: 今のサポートページと同じ Gmail を使う。案 B（URL を変える）は採らない前提。誰が Gmail を読むか（社長が読む／CCO 側で下書きまで、送信は社長）は社長判断。返信の目安日数も社長判断。CCO の窓口案は 10/2 まで（提出済み、と議事録）。設定画面から窓口へのリンクは v1 に含める。既存の仕組みを使える、と CTO。</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md 、https://github.com/naruto-aii/org-company/blob/main/CCO/ユーザー対応(Ldr)-アプリ事業部.md</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>公開URL</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>いま開く URL</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>議事録が参照する URL は naruto-aii.github.io/AYG/legal/ 。</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>main と web-preview の分け方</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
+      <c r="F53" s="4" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>公開URL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>いま開く URL</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>議事録が参照する URL は naruto-aii.github.io/AYG/legal/ 。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t>ブランチ・PR</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>議事録は PR #11 の合流に触れる。#25〜#29 の番号は書いていない。</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>返事の型は PR #11 合流後の実際の動きを基準にする、とある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
+          <t>main と web-preview の分け方</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -6927,12 +7071,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>古い Draft PR（#1 #11 #15 #16）</t>
+          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>PR #11 合流、という言及のみ。</t>
+          <t>議事録は PR #11 の合流に触れる。#25〜#29 の番号は書いていない。</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -6945,9 +7089,13 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="51" customHeight="1">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>返事の型は PR #11 合流後の実際の動きを基準にする、とある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -6955,436 +7103,484 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>マージ済みで先端に差が無いブランチ</t>
+          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>オープン PR は無い。マージ済みは #1 組織記録、#2 COO/CMO 目標、#3 カロナビ目標と運用ルール、#4 議事録3件、#5 書式、#6 議事録5件の全文、#7 Note 目標。main 以外の5ブランチは先行コミット 0。</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/org-company/pulls</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>ブランチ・PR</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>古い Draft PR（#1 #11 #15 #16）</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PR #11 合流、という言及のみ。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="51" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>ブランチ・PR</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>マージ済みで先端に差が無いブランチ</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>オープン PR は無い。マージ済みは #1 組織記録、#2 COO/CMO 目標、#3 カロナビ目標と運用ルール、#4 議事録3件、#5 書式、#6 議事録5件の全文、#7 Note 目標。main 以外の5ブランチは先行コミット 0。</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/pulls</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>開発状況</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>法務 README が「済んでいる」とするもの</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>CTO の現状欄は「記録なし（2026-09-27時点）」。完了／未完のチェックリストは議事録の期限として書かれる。</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/CTO/CTO.md</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="96" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="F60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="96" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>開発状況</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>実機未確認と残タスク</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>実機確認は 10/4〜5（ヘルスケア）。ヘルスケアを「連携」と書くのは 10/5 まで待つ、と CMO。デモアカウントは手順とサンプルを CTO が用意し、本番作成は 10/6、社長承認後。</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F59" s="3" t="n"/>
-    </row>
-    <row r="60" ht="66" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="F61" s="3" t="n"/>
+    </row>
+    <row r="62" ht="66" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>申請日</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>COO: 2026-10-09 までに App Store 申請。計画は 10/7 申請、10/8-9 予備。CTO 目標: 10/7 に審査に通る状態で申請できるようにする。提出準備の議事録: 10/7 に審査で落ちない状態で提出する（期限 10/9）。承認事項のとりまとめ締めは 10/3。</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/COO/COO.md 、https://github.com/naruto-aii/org-company/blob/main/CTO/CTO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="126" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="F62" s="2" t="n"/>
+    </row>
+    <row r="63" ht="126" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>10/1 前後の期限</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>10/1: カロナビ+ 購入画面（CTO-CPO）。CFO の値段案を COO へ。CPO の v1 範囲案を GM へ。Apple のキーを Supabase に登録（社長）。10/2: 禁止語フィルター。Apple 連携の取り消し。アイコン PNG を CTO へ。CCO の窓口案（提出済みと議事録）。10/3: 承認リストを社長補佐へ。v1 機能と有料範囲を承認可能な状態に（CPO）。料金体系案を承認可能な状態に（CFO）。Mac を使う日の候補に 10/3 と 10/6。</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>10/1: カロナビ+ 購入画面（CTO-CPO）。CFO の値段案を COO へ。CPO の v1 範囲案を GM へ。Apple のキーを Supabase に登録（社長）。10/2: 禁止語フィルター。Apple 連携の取り消し。アイコン PNG を CTO へ。CCO の窓口案（提出済みと議事録）。10/3: 承認リスト。窓口の議事録は「社長補佐へ」、COO 目標の現行文は「ゆりちゃんへ」。v1 機能と有料範囲を承認可能な状態に（CPO）。料金体系案を承認可能な状態に（CFO）。Mac を使う日の候補に 10/3 と 10/6。</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/技術本部（CTO）/2026-09-27_禁止語フィルターと購入画面.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/CPO/CPO.md 、https://github.com/naruto-aii/org-company/blob/main/CFO/CFO.md</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n"/>
-    </row>
-    <row r="62" ht="126" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="F63" s="3" t="n"/>
+    </row>
+    <row r="64" ht="126" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>10/4〜10/6 の期限</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>10/4〜5: ヘルスケアの実機確認（CPO）。10/5: App Privacy の回答案（CTO）。アイコンとスクリーンショット（CPO 目標）。ヘルスケアを「連携」と書くのを待つ期限（CMO）。10/6: デモアカウントの本番作成（社長承認後）。ストア掲載文（CMO）。健康表現と価格未定時の書き方を社長へ（CMO）。Mac の日の候補。</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/CPO/CPO.md 、https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n"/>
-    </row>
-    <row r="63" ht="66" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="66" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>目標</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>ダウンロード数</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>CMO 目標: 1か月目 1,000 人、半年 50,000 人、1年 500,000 人。2026-09-27 社長指示。現状欄は記録なし。獲得計画は確定 DL 0、数字は全て見込み。推奨は案 A（月 30 万円×3か月で単価と継続率を実測）。予算は未決定。1年目標を維持するか 90 日実測で見直すかは社長判断。</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n"/>
-    </row>
-    <row r="64" ht="66" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="F65" s="3" t="n"/>
+    </row>
+    <row r="66" ht="66" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>目標</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>利益</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>COO: 月の利益（カロナビ）は 3か月目 10 万円、半年 30 万円、1年 100 万円。GM の議事録上の見込み: 月 380 円、手数料 15% なら手取り約 323 円、費用を引く前でも約 310 人の有料会員。手数料が 15% かは未確認。上限を外すだけのカロナビ+ で届くかはデータが無く分からない、と GM。</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/COO/COO.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="126" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="F66" s="2" t="n"/>
+    </row>
+    <row r="67" ht="126" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>担当・体制</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>アプリ事業の役割</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>アプリ事業部の現在のプロダクトはカロナビ。GM-アプリ事業部、UIデザイナー(Ldr)、運用監視(Ldr)、獲得文章(Member)、ユーザー対応(Ldr)。役員目標: CPO は v1 と有料範囲（10/3）とアイコン・スクショ（10/5）。CTO は 10/7 に審査が通る状態。CFO は料金体系案（10/3）と経費の見える化。CMO は DL、獲得計画、掲載文（10/6）、価格決定後の LP。COO は申請進行と承認のとりまとめ。CCO 配下は問い合わせ。検査は作った人とは別の立場。本番反映とストア提出は社長の明示の承認までしない（CTO の役割）。現状欄は各役員とも記録なし。2026-09-27 の社長決定で秘書を廃止し、記録は34名。運用ルールは「社長に連絡できるのは社長補佐だけ」に更新された。</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>アプリ事業部の現在のプロダクトはカロナビ。GM-アプリ事業部、UIデザイナー(Ldr)、運用監視(Ldr)、獲得文章(Member)、ユーザー対応(Ldr)。役員目標: CPO は v1 と有料範囲（10/3）とアイコン・スクショ（10/5）。CTO は 10/7 に審査が通る状態。CFO は料金体系案（10/3）と経費の見える化。CMO は DL、獲得計画、掲載文（10/6）、価格決定後の LP。COO は申請進行と承認のとりまとめ。CCO 配下は問い合わせ。検査は作った人とは別の立場。本番反映とストア提出は社長の明示の承認までしない（CTO の役割）。現状欄は各役員とも記録なし。2026-09-27 の社長決定で秘書を廃止し、記録は34名。その後、社長補佐の名前はゆりちゃんに変わった（役割は同じ、と更新履歴）。運用ルールは「社長に連絡できるのはゆりちゃん（社長補佐）だけ」。</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/README.md 、https://github.com/naruto-aii/org-company/blob/main/COO/COO.md 、https://github.com/naruto-aii/org-company/blob/main/CPO/CPO.md 、https://github.com/naruto-aii/org-company/blob/main/CTO/CTO.md 、https://github.com/naruto-aii/org-company/blob/main/CFO/CFO.md 、https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md 、https://github.com/naruto-aii/org-company/blob/main/運用ルール.md</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>main 先端 9f6a176。運用ルール第2項は社長補佐だけ。秘書のファイルは削除済み。外に出すのは社長、と COO の役割。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>main 先端 0a779bc。ファイルは ゆりちゃん/ゆりちゃん.md。秘書のファイルは削除済み。外に出すのは社長、と COO の役割。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>2026-09-20 のプロダクト決定（AYG）</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>この日付の決定の写しは無い。9/27 の議事録が 380 円を「アプリに実装した値段」と呼ぶ。</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n"/>
-    </row>
-    <row r="67" ht="156" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="F68" s="2" t="n"/>
+    </row>
+    <row r="69" ht="156" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>CPO: v1 に自由な Web 閲覧、いいね・コメント、広告は入れない。禁止語フィルターを入れる（範囲は CTO 案）。境界案に GM が賛成。購入画面の 3.1.2 と公開後指標を完成条件に足す。決まった値段にアプリと LP の両方を合わせる。窓口は案 A 前提で CCO が案を作る。提出準備の技術分担（マニフェスト、Apple 取り消し、デモアカウント、App Privacy、アイコン書き出し）を CTO が引き受ける。獲得計画は案 A を推奨として提出済み（確定ではない）。ストア文の書き方（目安、非医療、有料プラン明記、ダイエットはキーワード可）は CMO 議事録の決定事項。</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/技術本部（CTO）/2026-09-27_禁止語フィルターと購入画面.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>CSO の 2026-09-27 議事録は新規事業案が主で、カロナビの決定は「なし」。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="141" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="70" ht="141" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>値段は 380 か 480 か（CFO が 10/1 に案、決めるのは社長、それまで表記は触らない）。年齢区分を 18+ にするか（CPO 推奨、未決）。獲得予算（案 A か他か）。1年 DL 目標を維持するか 90 日で見直すか。Gmail を誰が読むか。返信の目安日数。Mac を使う日（10/3 と 10/6）。Apple キーの登録。アイコン3案から1つ（9/30）。デモアカウントの本番作成の承認（10/6）。機能の確定、料金体系、有料範囲の承認（COO、締め 10/3）。健康表現と価格未定時の書き方（10/6）。小規模事業者プログラムで手数料 15% かは未確認。</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md 、https://github.com/naruto-aii/org-company/blob/main/COO/COO.md</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>各役員ファイルの「止まっていること」欄は記録なし。未決は議事録側に書いてある。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="36" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>食品出典の文書も UI ルールブックも改名の記録も無い。</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>既知の食い違い</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>ブランチによって README が違う</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>既知の食い違い</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>ハンドブックの更新日と中身</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
         </is>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
     </row>
-    <row r="72" ht="36" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UI デザイナーの役割説明のみ。納品物のファイルは無い。</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/CPO/UIデザイナー(Ldr)-アプリ事業部.md</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -7405,7 +7601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7741,20 +7937,20 @@
       <c r="F19" s="3" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>機能</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>運動記録・複数種目</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -8077,20 +8273,20 @@
       <c r="F40" s="4" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>法務</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>法務ページの置き場（2系統）</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プライバシー</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -8100,7 +8296,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>利用規約の記載</t>
+          <t>法務ページの置き場（2系統）</t>
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
@@ -8116,7 +8312,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>特定商取引法の記載</t>
+          <t>利用規約の記載</t>
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
@@ -8132,7 +8328,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>アカウント削除の法務文</t>
+          <t>特定商取引法の記載</t>
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
@@ -8143,12 +8339,12 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ストア</t>
+          <t>法務</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>掲載文・キーワード</t>
+          <t>アカウント削除の法務文</t>
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
@@ -8157,52 +8353,52 @@
       <c r="F45" s="4" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>掲載文・キーワード</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>スクリーンショット・アイコン</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>公開 URL とページの数</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>「App Storeで公開中」の表記</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>審査用デモアカウント</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -8212,7 +8408,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>価格の書き方</t>
+          <t>公開 URL とページの数</t>
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
@@ -8220,7 +8416,7 @@
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
     </row>
-    <row r="50" ht="36" customHeight="1">
+    <row r="50" ht="22" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>LP</t>
@@ -8228,7 +8424,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>機能説明の差（繰り越し・写真解析）</t>
+          <t>「App Storeで公開中」の表記</t>
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
@@ -8239,12 +8435,12 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>サポート</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>窓口のメールと URL</t>
+          <t>価格の書き方</t>
         </is>
       </c>
       <c r="C51" s="4" t="n"/>
@@ -8252,47 +8448,47 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>機能説明の差（繰り越し・写真解析）</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>サポート</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>窓口のメールと URL</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>公開URL</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>いま開く URL</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>main と web-preview の分け方</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
         </is>
       </c>
       <c r="C54" s="2" t="n"/>
@@ -8300,7 +8496,7 @@
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n"/>
     </row>
-    <row r="55" ht="36" customHeight="1">
+    <row r="55" ht="22" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -8308,7 +8504,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
+          <t>main と web-preview の分け方</t>
         </is>
       </c>
       <c r="C55" s="3" t="n"/>
@@ -8316,7 +8512,7 @@
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
     </row>
-    <row r="56" ht="22" customHeight="1">
+    <row r="56" ht="36" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -8324,7 +8520,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>古い Draft PR（#1 #11 #15 #16）</t>
+          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
         </is>
       </c>
       <c r="C56" s="2" t="n"/>
@@ -8340,7 +8536,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>マージ済みで先端に差が無いブランチ</t>
+          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
         </is>
       </c>
       <c r="C57" s="3" t="n"/>
@@ -8348,15 +8544,15 @@
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
     </row>
-    <row r="58" ht="36" customHeight="1">
+    <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>開発状況</t>
+          <t>ブランチ・PR</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>法務 README が「済んでいる」とするもの</t>
+          <t>古い Draft PR（#1 #11 #15 #16）</t>
         </is>
       </c>
       <c r="C58" s="2" t="n"/>
@@ -8364,15 +8560,15 @@
       <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="n"/>
     </row>
-    <row r="59" ht="22" customHeight="1">
+    <row r="59" ht="36" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>開発状況</t>
+          <t>ブランチ・PR</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>実機未確認と残タスク</t>
+          <t>マージ済みで先端に差が無いブランチ</t>
         </is>
       </c>
       <c r="C59" s="3" t="n"/>
@@ -8380,15 +8576,15 @@
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
     </row>
-    <row r="60" ht="22" customHeight="1">
+    <row r="60" ht="36" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>開発状況</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>申請日</t>
+          <t>法務 README が「済んでいる」とするもの</t>
         </is>
       </c>
       <c r="C60" s="2" t="n"/>
@@ -8399,12 +8595,12 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>開発状況</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>10/1 前後の期限</t>
+          <t>実機未確認と残タスク</t>
         </is>
       </c>
       <c r="C61" s="3" t="n"/>
@@ -8420,7 +8616,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>10/4〜10/6 の期限</t>
+          <t>申請日</t>
         </is>
       </c>
       <c r="C62" s="2" t="n"/>
@@ -8431,12 +8627,12 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ダウンロード数</t>
+          <t>10/1 前後の期限</t>
         </is>
       </c>
       <c r="C63" s="3" t="n"/>
@@ -8447,12 +8643,12 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>利益</t>
+          <t>10/4〜10/6 の期限</t>
         </is>
       </c>
       <c r="C64" s="2" t="n"/>
@@ -8463,12 +8659,12 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>担当・体制</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>アプリ事業の役割</t>
+          <t>ダウンロード数</t>
         </is>
       </c>
       <c r="C65" s="3" t="n"/>
@@ -8476,15 +8672,15 @@
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
     </row>
-    <row r="66" ht="36" customHeight="1">
+    <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
+          <t>利益</t>
         </is>
       </c>
       <c r="C66" s="2" t="n"/>
@@ -8492,15 +8688,15 @@
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
     </row>
-    <row r="67" ht="36" customHeight="1">
+    <row r="67" ht="22" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>担当・体制</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
+          <t>アプリ事業の役割</t>
         </is>
       </c>
       <c r="C67" s="3" t="n"/>
@@ -8509,30 +8705,30 @@
       <c r="F67" s="3" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>未決事項</t>
+          <t>決定事項</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>食品データの出典・UI ルールブック・改名</t>
+          <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
       <c r="C69" s="3" t="n"/>
@@ -8540,15 +8736,15 @@
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
     </row>
-    <row r="70" ht="22" customHeight="1">
+    <row r="70" ht="36" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ブランチによって README が違う</t>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
@@ -8556,15 +8752,15 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
     </row>
-    <row r="71" ht="22" customHeight="1">
+    <row r="71" ht="36" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ハンドブックの更新日と中身</t>
+          <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
       <c r="C71" s="3" t="n"/>
@@ -8573,23 +8769,55 @@
       <c r="F71" s="3" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -8610,7 +8838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9142,32 +9370,32 @@
       <c r="F19" s="3" t="n"/>
     </row>
     <row r="20" ht="66" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>機能</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>運動記録・複数種目</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>種目と時間からの MET 計算か、追加消費 kcal の手入力。ホームの残りに足すのは追加分だけ。通勤や家事のいつもの動きは生活活動の係数に含まれ、追加運動には入れない。対応端末では Apple ヘルスケアから歩数や運動を取り込める。ヘルスケアの当日消費カロリーは参考表示で、食事目標には足さない。</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -9650,32 +9878,24 @@
       <c r="F40" s="4" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>法務</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>法務ページの置き場（2系統）</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>法務リンクは naruto-aii.github.io/AYG/legal 。lp リポジトリ内に規約本文は無い。</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プライバシー</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>App Privacy の回答案</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -9685,12 +9905,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>利用規約の記載</t>
+          <t>法務ページの置き場（2系統）</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>条文は無く、公開法務 URL へリンク。</t>
+          <t>法務リンクは naruto-aii.github.io/AYG/legal 。lp リポジトリ内に規約本文は無い。</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -9713,12 +9933,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>特定商取引法の記載</t>
+          <t>利用規約の記載</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>特商法の本文は無い。料金はストア画面が正、と LP が書く。</t>
+          <t>条文は無く、公開法務 URL へリンク。</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -9741,121 +9961,113 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>アカウント削除の法務文</t>
+          <t>特定商取引法の記載</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
+          <t>特商法の本文は無い。料金はストア画面が正、と LP が書く。</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="F44" s="4" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ストア</t>
+          <t>法務</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>掲載文・キーワード</t>
+          <t>アカウント削除の法務文</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>LP はストア掲載文ではない。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
     </row>
-    <row r="46" ht="51" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>ストア</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>掲載文・キーワード</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>LP はストア掲載文ではない。</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="51" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>スクリーンショット・アイコン</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>写真9枚（hero-morning、morning-scale、barcode-scan、worry-fridge、worry-lunch、worry-gym、walk-street、evening-drink、quiet-return）と favicon.svg。ストアのスクリーンショット枠ではない。</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/blob/main/calonavi/img/ 、https://github.com/naruto-aii/lp/blob/main/calonavi/favicon.svg</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="51" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>公開 URL とページの数</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>README: カロナビは https://naruto-aii.github.io/lp/calonavi/ 。sitemap の loc も同じ。更新日 2026-09-25。</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/lp/blob/main/README.md 、https://github.com/naruto-aii/lp/blob/main/sitemap.xml 、https://naruto-aii.github.io/lp/calonavi/</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="51" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>「App Storeで公開中」の表記</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>「いつ使えますか？」は「App Storeで公開しています。このページからのストアリンクは、いま準備中です。」末尾も「App Storeで公開中です。ストアへのリンクは準備中です。」Information の提供欄も同じ。</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n"/>
+      <c r="F47" s="3" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ストア</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>審査用デモアカウント</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
     </row>
     <row r="49" ht="51" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -9865,167 +10077,183 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>公開 URL とページの数</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>README: カロナビは https://naruto-aii.github.io/lp/calonavi/ 。sitemap の loc も同じ。更新日 2026-09-25。</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/lp/blob/main/README.md 、https://github.com/naruto-aii/lp/blob/main/sitemap.xml 、https://naruto-aii.github.io/lp/calonavi/</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n"/>
+    </row>
+    <row r="50" ht="51" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>「App Storeで公開中」の表記</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>「いつ使えますか？」は「App Storeで公開しています。このページからのストアリンクは、いま準備中です。」末尾も「App Storeで公開中です。ストアへのリンクは準備中です。」Information の提供欄も同じ。</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="51" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>価格の書き方</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>金額は断定しない。有料機能の価格はストアの購入画面が正。無料枠の回数も書かない。</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>ページ内の更新日は 2026-09-25。コミットメッセージは Correct the Calonavi LP to shipped features only。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>機能説明の差（繰り越し・写真解析）</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>超過を翌日へ繰り越す機能は無い、と繰り返し書く。写真自動解析は実装されていない。未来の日付には記録できない。ゲスト利用は無い。</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="F52" s="4" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>サポート</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>窓口のメールと URL</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>問い合わせは同じ Gmail。サポートページの本文は置かず、法務 URL へリンク。</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>公開URL</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>いま開く URL</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>https://naruto-aii.github.io/lp/calonavi/ （200）。</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/lp/blob/main/README.md 、https://github.com/naruto-aii/lp/blob/main/.github/workflows/pages.yml</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>pages.yml は main への push でリポジトリ全体を GitHub Pages に出す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>main と web-preview の分け方</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
+      <c r="F53" s="4" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>公開URL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>いま開く URL</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>https://naruto-aii.github.io/lp/calonavi/ （200）。</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/lp/blob/main/README.md 、https://github.com/naruto-aii/lp/blob/main/.github/workflows/pages.yml</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>pages.yml は main への push でリポジトリ全体を GitHub Pages に出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t>ブランチ・PR</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>ブランチ・PR</t>
-        </is>
-      </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
+          <t>main と web-preview の分け方</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -10037,7 +10265,7 @@
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
     </row>
-    <row r="56" ht="22" customHeight="1">
+    <row r="56" ht="36" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>ブランチ・PR</t>
@@ -10045,7 +10273,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>古い Draft PR（#1 #11 #15 #16）</t>
+          <t>オープンな Draft PR（#25〜#29 の積み重ね）</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -10065,103 +10293,103 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
+          <t>#25 と #26 にあって旧 #28 に無かった4コミット</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ブランチ・PR</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>古い Draft PR（#1 #11 #15 #16）</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>ブランチ・PR</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>マージ済みで先端に差が無いブランチ</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>PR は 0。main のみ。</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/pulls</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n"/>
-    </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="F59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>開発状況</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>法務 README が「済んでいる」とするもの</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>LP の「いまできること」は出荷済み機能だけ、というコミットメッセージ。コードの完了判定は書いていない。</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/lp/blob/main のコミット 4f44f69</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>開発状況</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>実機未確認と残タスク</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>申請日</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>開発状況</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>10/1 前後の期限</t>
+          <t>実機未確認と残タスク</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -10181,7 +10409,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>10/4〜10/6 の期限</t>
+          <t>申請日</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -10196,12 +10424,12 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ダウンロード数</t>
+          <t>10/1 前後の期限</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -10216,12 +10444,12 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>目標</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>利益</t>
+          <t>10/4〜10/6 の期限</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -10236,12 +10464,12 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>担当・体制</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>アプリ事業の役割</t>
+          <t>ダウンロード数</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -10253,15 +10481,15 @@
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
     </row>
-    <row r="66" ht="36" customHeight="1">
+    <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>目標</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
+          <t>利益</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -10273,15 +10501,15 @@
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
     </row>
-    <row r="67" ht="36" customHeight="1">
+    <row r="67" ht="22" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>担当・体制</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
+          <t>アプリ事業の役割</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10294,87 +10522,87 @@
       <c r="F67" s="3" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>金額は未記載（断定しない、と書くだけ）。</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>未決事項</t>
+          <t>決定事項</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>食品データの出典・UI ルールブック・改名</t>
+          <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>出典の文書は無い。名称はカロナビのまま。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
     </row>
-    <row r="70" ht="22" customHeight="1">
+    <row r="70" ht="36" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ブランチによって README が違う</t>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
+          <t>金額は未記載（断定しない、と書くだけ）。</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="n"/>
     </row>
-    <row r="71" ht="22" customHeight="1">
+    <row r="71" ht="36" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ハンドブックの更新日と中身</t>
+          <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>記載なし。</t>
+          <t>出典の文書は無い。名称はカロナビのまま。</t>
         </is>
       </c>
       <c r="D71" s="3" t="n"/>
@@ -10382,27 +10610,67 @@
       <c r="F71" s="3" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/カロナビ/2026-09-28_カロナビ_リポジトリ別現状整理.xlsx
+++ b/カロナビ/2026-09-28_カロナビ_リポジトリ別現状整理.xlsx
@@ -14,15 +14,15 @@
     <sheet name="lp" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'差分まとめ'!$A$1:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'差分まとめ'!$A$1:$H$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'差分まとめ'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AYG'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AYG'!$A$1:$F$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'AYG'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'org-company'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'org-company'!$A$1:$F$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'org-company'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'company-os'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'company-os'!$A$1:$F$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'company-os'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'lp'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'lp'!$A$1:$F$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'lp'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3500,62 +3500,62 @@
       </c>
     </row>
     <row r="80" ht="180" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>獲得計画草案の広告費</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>作業ファイル/2026-09-27/calonavi/acquisition_plan_draft.md。社長確認前の案。確定DLは0。1か月目1,000DLは、広告なしでは高位（自然流入が月1,500）のときだけ届く。中位は約21万円、低位は約63万円の有料獲得が要る、と書く。半年50,000DLの広告費は約740万円（高位）〜約1,940万円（中位）〜約3,630万円（低位）。1年500,000DLは中位で広告費約2.0億円、すべて有料なら約2.2億〜4.8億円。あすけんの年間会員純増は約180万人（iOS＋Android）で、1年目標はその約3割、と書く。提案は最初の3か月を月30万円（案A）。公開は10月中旬以降と仮定。訴求の軸にヘルスケア連携と Google/Apple ログインを含む。価格は未定で LTV は計算できない、と書く。為替は1ドル＝150円の仮定。</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>予算の幅は org のこの草案だけ。訴求の軸にヘルスケア連携と Google ログインを書いており、CMO 議事録の「10/5 まで連携と書かない」と、v1範囲案の「Google は含めない」と並ぶ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="180" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>担当・体制</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>アプリ事業の役割</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>記載なし（組織図は無い）。法務 README の括弧書き担当: Google/Health の実機は Owner、不具合はエージェント、掲載テキストは Owner、見た目はエージェント、スクショは Owner（素材はデザイナー）、TestFlight は Owner。</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>アプリ事業部の現在のプロダクトはカロナビ。GM-アプリ事業部、UIデザイナー(Ldr)、運用監視(Ldr)、獲得文章(Member)、ユーザー対応(Ldr)。役員目標: CPO は v1 と有料範囲（10/3）とアイコン・スクショ（10/5）。CTO は 10/7 に審査が通る状態。CFO は料金体系案（10/3）と経費の見える化。CMO は DL、獲得計画、掲載文（10/6）、価格決定後の LP。COO は申請進行と承認のとりまとめ。CCO 配下は問い合わせ。検査は作った人とは別の立場。本番反映とストア提出は社長の明示の承認までしない（CTO の役割）。現状欄は各役員とも記録なし。2026-09-27 の社長決定で秘書を廃止し、記録は34名。その後、社長補佐の名前はゆりちゃんに変わった（役割は同じ、と更新履歴）。運用ルールは「社長に連絡できるのはゆりちゃん（社長補佐）だけ」。</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>一部にしか記載なし</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>体制は org-company。AYG は Owner とエージェントとデザイナー、という残タスクの担当だけ。秘書廃止はカロナビの機能仕様ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="66" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>担当・体制</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>組織図の画像</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>組織図の画像は無い。</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>制作物/全社/組織図/orgchart.png。README: 2026-09-27 の図。図中は秘書廃止前・社長補佐改名前の表記。状態は案。運用ルールの現行文は、社長に連絡できるのはゆりちゃん（社長補佐）だけ。</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3571,29 +3571,29 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>画像の表記と、その後の運用ルールの表記がファイル自身の説明で違う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="96" customHeight="1">
+          <t>体制は org-company。AYG は Owner とエージェントとデザイナー、という残タスクの担当だけ。秘書廃止はカロナビの機能仕様ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="66" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>担当・体制</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
+          <t>組織図の画像</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
+          <t>組織図の画像は無い。</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>この日付の決定の写しは無い。9/27 の議事録が 380 円を「アプリに実装した値段」と呼ぶ。</t>
+          <t>制作物/全社/組織図/orgchart.png。README: 2026-09-27 の図。図中は秘書廃止前・社長補佐改名前の表記。状態は案。運用ルールの現行文は、社長に連絡できるのはゆりちゃん（社長補佐）だけ。</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3609,219 +3609,219 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
+          <t>画像の表記と、その後の運用ルールの表記がファイル自身の説明で違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="81" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>担当・体制</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>note初記事の体制の書き方</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>作業ファイル/2026-09-27/media/note/01_first/final.md。社長の下に「社長補佐（社長室長）」がいる、と書く。別枠で「秘書」もいる、と書く。【社長記入待ち】の欄がある。運用ルールの現行文は、秘書を廃止し、社長に連絡できるのはゆりちゃん（社長補佐）だけ。</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>note の確定稿下書きは秘書と社長補佐（社長室長）を書く。その後の運用ルールは秘書廃止と、名前をゆりちゃんに変えた記録。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="96" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>この日付の決定の写しは無い。9/27 の議事録が 380 円を「アプリに実装した値段」と呼ぶ。</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>一部にしか記載なし</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
           <t>9/20 の決定文は AYG の法務 README。9/27 の org は値段を未決として扱っている（次の未決の行）。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="156" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="85" ht="156" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>CPO: v1 に自由な Web 閲覧、いいね・コメント、広告は入れない。禁止語フィルターを入れる（範囲は CTO 案）。境界案に GM が賛成。購入画面の 3.1.2 と公開後指標を完成条件に足す。決まった値段にアプリと LP の両方を合わせる。窓口は案 A 前提で CCO が案を作る。提出準備の技術分担（マニフェスト、Apple 取り消し、デモアカウント、App Privacy、アイコン書き出し）を CTO が引き受ける。獲得計画は案 A を推奨として提出済み（確定ではない）。ストア文の書き方（目安、非医療、有料プラン明記、ダイエットはキーワード可）は CMO 議事録の決定事項。</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>一部にしか記載なし</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>組織の決定は org-company。AYG はそれに対応する未マージのコードがある、という関係。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="180" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>値段は 380 か 480 か。CFO の比較案は出ているが「この数字で判断してよいか：まだ不可」。決めるのは社長。年齢区分を 18+ にするか（v1範囲案も CPO 推奨、未決）。獲得予算（案 A か他か）。1年 DL 目標を維持するか 90 日で見直すか。Gmail を誰が読むか。返信の目安日数。返金の補足方針（返事の型は Apple の手続き案内のみで、当方の方針は社長判断待ち）。Mac を使う日（10/3 と 10/6）。Apple キーの登録。アイコン3案から1つ（9/30。画像は制作物にあるが選定前）。デモアカウントの本番作成の承認（10/6）。機能の確定、料金体系、有料範囲の承認（COO、締め 10/3）。健康表現と価格未定時の書き方（10/6）。小規模事業者プログラムで手数料 15% かは未確認。為替 $1＝¥150 は仮置き。Google サインインを v1 から外すかは v1範囲案に書いてあり、議事録の決定としては無い。</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>金額は未記載（断定しない、と書くだけ）。</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>食い違い</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>未決であることは org が明示。同時に AYG の公開 LP は 480 円を予定価格として出し、社内メモと ASC の記載は 380 円。CFO は決まるまで表記を変えるな、と言っているので、二つの数字が並んだまま。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="66" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>食品データの出典・UI ルールブック・改名</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>Open Food Facts をバーコードの取得元にする、と 01_Project。食品データベースの出典一覧や外食 DB の制約文書は、読んだブランチには無い。UI ルールブックというファイルも無い。カロリードへの改名の文字列は全コミットで 0 件。</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>食品出典の文書も UI ルールブックも改名の記録も無い。</t>
         </is>
       </c>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>一部にしか記載なし</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>組織の決定は org-company。AYG はそれに対応する未マージのコードがある、という関係。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="180" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>未決事項</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>値段は 380 か 480 か。CFO の比較案は出ているが「この数字で判断してよいか：まだ不可」。決めるのは社長。年齢区分を 18+ にするか（v1範囲案も CPO 推奨、未決）。獲得予算（案 A か他か）。1年 DL 目標を維持するか 90 日で見直すか。Gmail を誰が読むか。返信の目安日数。返金の補足方針（返事の型は Apple の手続き案内のみで、当方の方針は社長判断待ち）。Mac を使う日（10/3 と 10/6）。Apple キーの登録。アイコン3案から1つ（9/30。画像は制作物にあるが選定前）。デモアカウントの本番作成の承認（10/6）。機能の確定、料金体系、有料範囲の承認（COO、締め 10/3）。健康表現と価格未定時の書き方（10/6）。小規模事業者プログラムで手数料 15% かは未確認。為替 $1＝¥150 は仮置き。Google サインインを v1 から外すかは v1範囲案に書いてあり、議事録の決定としては無い。</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>金額は未記載（断定しない、と書くだけ）。</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>未決であることは org が明示。同時に AYG の公開 LP は 480 円を予定価格として出し、社内メモと ASC の記載は 380 円。CFO は決まるまで表記を変えるな、と言っているので、二つの数字が並んだまま。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="66" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>未決事項</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>食品データの出典・UI ルールブック・改名</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Open Food Facts をバーコードの取得元にする、と 01_Project。食品データベースの出典一覧や外食 DB の制約文書は、読んだブランチには無い。UI ルールブックというファイルも無い。カロリードへの改名の文字列は全コミットで 0 件。</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>食品出典の文書も UI ルールブックも改名の記録も無い。</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
           <t>出典の文書は無い。名称はカロナビのまま。</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>どこにも記載なし</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>読めた3リポジトリには、食品出典の専用文書、UI ルールブック、カロリードへの改名は無かった。company-os は未読なので、そこにあるかどうかは今回判定できない。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="96" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88" ht="96" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>オーナー方針メモ（未記入）</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Vision/Mission などは 01_Project の Open Question。方針メモそのものは無い。</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>作業ファイル/2026-09-27/calonavi-owner-policy-template.md と INDEX。作成 2026-09-20。方針欄はすべて未記入。項目は 103。カテゴリはビジョン、デザイン、栄養と Health、認証、アカウント削除、IAP、ストア、審査日程、サポート、データ、公開食品、法務、法人化、マーケ、外部協力、開発運用。</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>一部にしか記載なし</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>未記入の質問一覧は org-company の作業ファイルだけ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="36" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>既知の食い違い</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>ブランチによって README が違う</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>main の README は Flutter の初期文だけ。web-preview と #29 は先頭にカロナビの説明と公開 URL。既定ブランチは main。</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>食い違い</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>同じリポジトリの main とアプリ側ブランチで、最初に見える説明が違う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="81" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>既知の食い違い</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>ハンドブックの更新日と中身</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>docs/01_Project.md と docs/02_System_Architecture.md のヘッダは Last updated: 2026-07-22、Status は Version 1.1（承認済み）。git の最終更新は 2026-09-20。本文は 9 月の残タスク（docs/legal/README.md を参照）を含む。Decision Log の実ファイルは 0 バイトのまま。</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
@@ -3837,51 +3837,127 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
+          <t>未記入の質問一覧は org-company の作業ファイルだけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>main の README は Flutter の初期文だけ。web-preview と #29 は先頭にカロナビの説明と公開 URL。既定ブランチは main。</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>食い違い</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>同じリポジトリの main とアプリ側ブランチで、最初に見える説明が違う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="81" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>docs/01_Project.md と docs/02_System_Architecture.md のヘッダは Last updated: 2026-07-22、Status は Version 1.1（承認済み）。git の最終更新は 2026-09-20。本文は 9 月の残タスク（docs/legal/README.md を参照）を含む。Decision Log の実ファイルは 0 バイトのまま。</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>一部にしか記載なし</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
           <t>AYG の中で、文書の自己申告の日付と git の日付と、空の Decision Log が並んでいる。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="96" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="91" ht="96" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>web-preview と #29 にあるデザイン資料は docs/design/README.md と 03_WORKOUT_INPUT.md。00_DESIGNER_BRIEF.md、01_INFORMATION_ARCHITECTURE.md、02_DELIVERABLES.md は PR #1 のブランチだけ。FIGMA の見た目コミットは PR #16 にあり、#29 には入っていない。デザイン README は実装の正を web-preview ブランチとしている（#29 ではない）。</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>UI デザイナーの役割説明のみ。納品物のファイルは無い。</t>
         </is>
       </c>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>一部にしか記載なし</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>デザインの正が web-preview と書かれたまま、新しいコードは #25〜#29 に積まれ、Figma 適用の2コミットは #16 に残っている。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H89">
-    <sortState ref="A1:H89">
+  <autoFilter ref="A1:H91">
+    <sortState ref="A1:H91">
       <sortCondition descending="0" ref="A2:A1000"/>
     </sortState>
   </autoFilter>
@@ -3905,7 +3981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6252,284 +6328,324 @@
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
     </row>
-    <row r="80" ht="51" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>獲得計画草案の広告費</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+    </row>
+    <row r="81" ht="51" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>担当・体制</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>アプリ事業の役割</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>記載なし（組織図は無い）。法務 README の括弧書き担当: Google/Health の実機は Owner、不具合はエージェント、掲載テキストは Owner、見た目はエージェント、スクショは Owner（素材はデザイナー）、TestFlight は Owner。</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F80" s="2" t="n"/>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="F81" s="3" t="n"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>担当・体制</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>組織図の画像</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>組織図の画像は無い。</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-    </row>
-    <row r="82" ht="66" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>担当・体制</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>note初記事の体制の書き方</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="66" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>2026-09-20 のプロダクト決定（AYG）</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>初回公開は App Store のみ。Google Play は出さない。運営は法人化まで個人・麹池成。アカウント削除後の公開食品は残し、作成者欄は「削除済みユーザー」。法務文面は弁護士未確認のまま出す。課金はカロナビ+、月 380 円／年 4,180 円を社内の商品決定のメモとし、公開特商法は金額を固定しない。Product ID 二つ。無料枠 5/3/3。記録・Health・バーコード・公開投稿は無料。</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>見出しは「課金（2026-09-20 決定）」。ファイルの git 更新は 2026-09-27。</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="51" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>決定事項</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/28 https://github.com/naruto-aii/AYG/pull/29</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n"/>
-    </row>
-    <row r="84" ht="81" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n"/>
     </row>
     <row r="85" ht="51" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27 の議事録で決まったこと</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>コード側では、禁止語マイグレーション、購入画面の StoreKit 価格と自動更新と規約リンク、利用状況の記録、iPhone 限定と Privacy manifest、Apple トークン失効の関数が Draft PR としてある。マージしない、本番に当てない、と各 PR が書く。</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/pull/26 https://github.com/naruto-aii/AYG/pull/27 https://github.com/naruto-aii/AYG/pull/28 https://github.com/naruto-aii/AYG/pull/29</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n"/>
+    </row>
+    <row r="86" ht="81" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>01_Project の Open Question: Vision/Mission、Core Value の具体例、体重タブの本格 UI、Health Workout の反映、Google Play を出す時期。法務 README は値段の最終を App Store 画面に寄せ、社内メモは 380/4,180。公開 LP は 480/4,800 のまま。</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/legal/README.md 、https://github.com/naruto-aii/AYG/blob/main/docs/index.html</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n"/>
+    </row>
+    <row r="87" ht="51" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>未決事項</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Open Food Facts をバーコードの取得元にする、と 01_Project。食品データベースの出典一覧や外食 DB の制約文書は、読んだブランチには無い。UI ルールブックというファイルも無い。カロリードへの改名の文字列は全コミットで 0 件。</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>git log -S カロリード と Calolead は AYG・org-company・lp で 0 件。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>オーナー方針メモ（未記入）</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Vision/Mission などは 01_Project の Open Question。方針メモそのものは無い。</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-    </row>
-    <row r="87" ht="51" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+    </row>
+    <row r="89" ht="51" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ブランチによって README が違う</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>main の README は Flutter の初期文だけ。web-preview と #29 は先頭にカロナビの説明と公開 URL。既定ブランチは main。</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/main/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/README.md</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>main の README の git は 2026-07-21。アプリ側 README の git は 2026-09-25。</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="96" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90" ht="96" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>ハンドブックの更新日と中身</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>docs/01_Project.md と docs/02_System_Architecture.md のヘッダは Last updated: 2026-07-22、Status は Version 1.1（承認済み）。git の最終更新は 2026-09-20。本文は 9 月の残タスク（docs/legal/README.md を参照）を含む。Decision Log の実ファイルは 0 バイトのまま。</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/01_Project.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/02_System_Architecture.md 、https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/05_DECISION_LOG.md</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F88" s="2" t="n"/>
-    </row>
-    <row r="89" ht="66" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="F90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="66" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>web-preview と #29 にあるデザイン資料は docs/design/README.md と 03_WORKOUT_INPUT.md。00_DESIGNER_BRIEF.md、01_INFORMATION_ARCHITECTURE.md、02_DELIVERABLES.md は PR #1 のブランチだけ。FIGMA の見た目コミットは PR #16 にあり、#29 には入っていない。デザイン README は実装の正を web-preview ブランチとしている（#29 ではない）。</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/AYG/blob/cursor/apple-token-revoke-on-delete-eb80/docs/design/README.md 、https://github.com/naruto-aii/AYG/blob/cursor/designer-brief-08a9/docs/design/00_DESIGNER_BRIEF.md 、https://github.com/naruto-aii/AYG/pull/16</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6550,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8726,275 +8842,335 @@
       <c r="F79" s="3" t="n"/>
     </row>
     <row r="80" ht="126" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>獲得計画草案の広告費</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>作業ファイル/2026-09-27/calonavi/acquisition_plan_draft.md。社長確認前の案。確定DLは0。1か月目1,000DLは、広告なしでは高位（自然流入が月1,500）のときだけ届く。中位は約21万円、低位は約63万円の有料獲得が要る、と書く。半年50,000DLの広告費は約740万円（高位）〜約1,940万円（中位）〜約3,630万円（低位）。1年500,000DLは中位で広告費約2.0億円、すべて有料なら約2.2億〜4.8億円。あすけんの年間会員純増は約180万人（iOS＋Android）で、1年目標はその約3割、と書く。提案は最初の3か月を月30万円（案A）。公開は10月中旬以降と仮定。訴求の軸にヘルスケア連携と Google/Apple ログインを含む。価格は未定で LTV は計算できない、と書く。為替は1ドル＝150円の仮定。</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/作業ファイル/2026-09-27/calonavi/acquisition_plan_draft.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md 、https://github.com/naruto-aii/org-company/blob/main/制作物/アプリ事業部/v1範囲案/2026-09-27_v1範囲案.md</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>CMO 議事録の推奨も案A（月30万円×3か月）。広告費の幅の数字は作業ファイル側。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="126" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>担当・体制</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>アプリ事業の役割</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>アプリ事業部の現在のプロダクトはカロナビ。GM-アプリ事業部、UIデザイナー(Ldr)、運用監視(Ldr)、獲得文章(Member)、ユーザー対応(Ldr)。役員目標: CPO は v1 と有料範囲（10/3）とアイコン・スクショ（10/5）。CTO は 10/7 に審査が通る状態。CFO は料金体系案（10/3）と経費の見える化。CMO は DL、獲得計画、掲載文（10/6）、価格決定後の LP。COO は申請進行と承認のとりまとめ。CCO 配下は問い合わせ。検査は作った人とは別の立場。本番反映とストア提出は社長の明示の承認までしない（CTO の役割）。現状欄は各役員とも記録なし。2026-09-27 の社長決定で秘書を廃止し、記録は34名。その後、社長補佐の名前はゆりちゃんに変わった（役割は同じ、と更新履歴）。運用ルールは「社長に連絡できるのはゆりちゃん（社長補佐）だけ」。</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/README.md 、https://github.com/naruto-aii/org-company/blob/main/COO/COO.md 、https://github.com/naruto-aii/org-company/blob/main/CPO/CPO.md 、https://github.com/naruto-aii/org-company/blob/main/CTO/CTO.md 、https://github.com/naruto-aii/org-company/blob/main/CFO/CFO.md 、https://github.com/naruto-aii/org-company/blob/main/CMO/CMO.md 、https://github.com/naruto-aii/org-company/blob/main/運用ルール.md</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>main 先端 df0955d（作業ファイルのバックアップ）。ファイルは ゆりちゃん/ゆりちゃん.md。秘書のファイルは削除済み。外に出すのは社長、と COO の役割。制作物 README: 全Botの制作物は 制作物/ に集約。作ったBotは /workspace/制作物-queue/ に置き、ゆりちゃんが反映する。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="51" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="82" ht="51" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>担当・体制</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>組織図の画像</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>制作物/全社/組織図/orgchart.png。README: 2026-09-27 の図。図中は秘書廃止前・社長補佐改名前の表記。状態は案。運用ルールの現行文は、社長に連絡できるのはゆりちゃん（社長補佐）だけ。</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/制作物/README.md 、https://github.com/naruto-aii/org-company/blob/main/運用ルール.md</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F81" s="3" t="n"/>
-    </row>
-    <row r="82" ht="36" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83" ht="51" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>担当・体制</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>note初記事の体制の書き方</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>作業ファイル/2026-09-27/media/note/01_first/final.md。社長の下に「社長補佐（社長室長）」がいる、と書く。別枠で「秘書」もいる、と書く。【社長記入待ち】の欄がある。運用ルールの現行文は、秘書を廃止し、社長に連絡できるのはゆりちゃん（社長補佐）だけ。</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/org-company/blob/main/作業ファイル/2026-09-27/media/note/01_first/final.md 、https://github.com/naruto-aii/org-company/blob/main/運用ルール.md</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>2026-09-20 のプロダクト決定（AYG）</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>この日付の決定の写しは無い。9/27 の議事録が 380 円を「アプリに実装した値段」と呼ぶ。</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F82" s="2" t="n"/>
-    </row>
-    <row r="83" ht="156" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="F84" s="2" t="n"/>
+    </row>
+    <row r="85" ht="156" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>CPO: v1 に自由な Web 閲覧、いいね・コメント、広告は入れない。禁止語フィルターを入れる（範囲は CTO 案）。境界案に GM が賛成。購入画面の 3.1.2 と公開後指標を完成条件に足す。決まった値段にアプリと LP の両方を合わせる。窓口は案 A 前提で CCO が案を作る。提出準備の技術分担（マニフェスト、Apple 取り消し、デモアカウント、App Privacy、アイコン書き出し）を CTO が引き受ける。獲得計画は案 A を推奨として提出済み（確定ではない）。ストア文の書き方（目安、非医療、有料プラン明記、ダイエットはキーワード可）は CMO 議事録の決定事項。</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/技術本部（CTO）/2026-09-27_禁止語フィルターと購入画面.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>CSO の 2026-09-27 議事録は新規事業案が主で、カロナビの決定は「なし」。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="141" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="86" ht="141" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>値段は 380 か 480 か。CFO の比較案は出ているが「この数字で判断してよいか：まだ不可」。決めるのは社長。年齢区分を 18+ にするか（v1範囲案も CPO 推奨、未決）。獲得予算（案 A か他か）。1年 DL 目標を維持するか 90 日で見直すか。Gmail を誰が読むか。返信の目安日数。返金の補足方針（返事の型は Apple の手続き案内のみで、当方の方針は社長判断待ち）。Mac を使う日（10/3 と 10/6）。Apple キーの登録。アイコン3案から1つ（9/30。画像は制作物にあるが選定前）。デモアカウントの本番作成の承認（10/6）。機能の確定、料金体系、有料範囲の承認（COO、締め 10/3）。健康表現と価格未定時の書き方（10/6）。小規模事業者プログラムで手数料 15% かは未確認。為替 $1＝¥150 は仮置き。Google サインインを v1 から外すかは v1範囲案に書いてあり、議事録の決定としては無い。</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/議事録/プロダクト本部（CPO）/2026-09-27_カロナビ.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビ提出準備の分担.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/アプリ事業部 幹部会/2026-09-27_カロナビの問い合わせ窓口.md 、https://github.com/naruto-aii/org-company/blob/main/議事録/マーケティング本部（CMO）/2026-09-27_カロナビ獲得計画・ストア掲載文.md 、https://github.com/naruto-aii/org-company/blob/main/COO/COO.md</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>各役員ファイルの「止まっていること」欄は記録なし。未決は議事録側に書いてある。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="36" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>食品データの出典・UI ルールブック・改名</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>食品出典の文書も UI ルールブックも改名の記録も無い。</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-    </row>
-    <row r="86" ht="66" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+    </row>
+    <row r="88" ht="66" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>オーナー方針メモ（未記入）</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>作業ファイル/2026-09-27/calonavi-owner-policy-template.md と INDEX。作成 2026-09-20。方針欄はすべて未記入。項目は 103。カテゴリはビジョン、デザイン、栄養と Health、認証、アカウント削除、IAP、ストア、審査日程、サポート、データ、公開食品、法務、法人化、マーケ、外部協力、開発運用。</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/作業ファイル/2026-09-27/calonavi-owner-policy-template-INDEX.md</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F86" s="2" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="F88" s="2" t="n"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ブランチによって README が違う</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>ハンドブックの更新日と中身</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
-    </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>UI デザイナーの役割説明のみ。納品物のファイルは無い。</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>https://github.com/naruto-aii/org-company/blob/main/CPO/UIデザイナー(Ldr)-アプリ事業部.md</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -9015,7 +9191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10311,20 +10487,20 @@
       <c r="F79" s="3" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>担当・体制</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>アプリ事業の役割</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>獲得計画草案の広告費</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -10334,7 +10510,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>組織図の画像</t>
+          <t>アプリ事業の役割</t>
         </is>
       </c>
       <c r="C81" s="3" t="n"/>
@@ -10342,15 +10518,15 @@
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
     </row>
-    <row r="82" ht="36" customHeight="1">
+    <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>担当・体制</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
+          <t>組織図の画像</t>
         </is>
       </c>
       <c r="C82" s="2" t="n"/>
@@ -10358,47 +10534,47 @@
       <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n"/>
     </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>担当・体制</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>note初記事の体制の書き方</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>未決事項</t>
+          <t>決定事項</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>食品データの出典・UI ルールブック・改名</t>
+          <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
       <c r="C85" s="3" t="n"/>
@@ -10406,47 +10582,47 @@
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>オーナー方針メモ（未記入）</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>既知の食い違い</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>ブランチによって README が違う</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>未決事項</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>食品データの出典・UI ルールブック・改名</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ハンドブックの更新日と中身</t>
+          <t>オーナー方針メモ（未記入）</t>
         </is>
       </c>
       <c r="C88" s="2" t="n"/>
@@ -10455,23 +10631,55 @@
       <c r="F88" s="2" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10492,7 +10700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12416,24 +12624,24 @@
       <c r="F79" s="3" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>担当・体制</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>アプリ事業の役割</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>獲得計画草案の広告費</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -12443,7 +12651,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>組織図の画像</t>
+          <t>アプリ事業の役割</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -12455,15 +12663,15 @@
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
     </row>
-    <row r="82" ht="36" customHeight="1">
+    <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>担当・体制</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 のプロダクト決定（AYG）</t>
+          <t>組織図の画像</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12475,123 +12683,123 @@
       <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n"/>
     </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>担当・体制</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>note初記事の体制の書き方</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>決定事項</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-27 の議事録で決まったこと</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 のプロダクト決定（AYG）</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>未決事項</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>金額は未記載（断定しない、と書くだけ）。</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>未決事項</t>
+          <t>決定事項</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>食品データの出典・UI ルールブック・改名</t>
+          <t>2026-09-27 の議事録で決まったこと</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>出典の文書は無い。名称はカロナビのまま。</t>
+          <t>記載なし。</t>
         </is>
       </c>
       <c r="D85" s="3" t="n"/>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>未決事項</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>オーナー方針メモ（未記入）</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>既知の食い違い</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>ブランチによって README が違う</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>記載なし。</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>社長の判断待ち（値段・年齢・予算・窓口）</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>金額は未記載（断定しない、と書くだけ）。</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/naruto-aii/lp/blob/main/calonavi/index.html</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n"/>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>未決事項</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>食品データの出典・UI ルールブック・改名</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>出典の文書は無い。名称はカロナビのまま。</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>既知の食い違い</t>
+          <t>未決事項</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ハンドブックの更新日と中身</t>
+          <t>オーナー方針メモ（未記入）</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -12604,27 +12812,67 @@
       <c r="F88" s="2" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>既知の食い違い</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>ブランチによって README が違う</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ハンドブックの更新日と中身</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>記載なし。</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>既知の食い違い</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>デザイナー資料の置き場</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>記載なし。</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
